--- a/Datas/EmoteData.xlsx
+++ b/Datas/EmoteData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -232,6 +232,10 @@
   </si>
   <si>
     <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>倒计时</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -557,7 +561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:E47"/>
+  <dimension ref="A2:E48"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="14.625" customWidth="1"/>
@@ -1345,6 +1349,23 @@
         <v>60</v>
       </c>
     </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>72</v>
+      </c>
+      <c r="B48" t="s">
+        <v>54</v>
+      </c>
+      <c r="C48">
+        <v>72</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="E48">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Datas/EmoteData.xlsx
+++ b/Datas/EmoteData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="180">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -237,6 +237,457 @@
   <si>
     <t>倒计时</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>法阵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多角星</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>四芒星</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>咬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文字</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>曲谱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数字</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计算符号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多云</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>太阳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷雨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大雨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雪人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>彩虹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>月亮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>面包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>肉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蘑菇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>苹果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蛋糕</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>茶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>啤酒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>信</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>翻书</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>炸弹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>锤子砸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>按钮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>钻石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一箱子金币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金币</t>
+  </si>
+  <si>
+    <t>礼物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奖杯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奖牌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>王冠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>天使</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恶魔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幽灵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>便便</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拳头</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>剪刀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>向上箭头</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>下降箭头</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑桃</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>红心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>梅花</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>方片</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>男性标志</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>女性标志</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>o标志</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>x标志</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>三角</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>矩形</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>箭头上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>箭头下</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>箭头左</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>箭头右</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>箭头左上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>箭头右上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>箭头左下</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>箭头右下</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>窄三角三</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宽三角三</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白色三角上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白色三角下</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白色三角左</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白色三角右</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白色三角左上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白色三角右上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白色三角左下</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白色三角右下</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白色骰子123</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白色骰子456</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>红色三角上</t>
+  </si>
+  <si>
+    <t>红色三角下</t>
+  </si>
+  <si>
+    <t>红色三角左</t>
+  </si>
+  <si>
+    <t>红色三角右</t>
+  </si>
+  <si>
+    <t>红色三角左上</t>
+  </si>
+  <si>
+    <t>红色三角右上</t>
+  </si>
+  <si>
+    <t>红色三角左下</t>
+  </si>
+  <si>
+    <t>红色三角右下</t>
+  </si>
+  <si>
+    <t>黑色骰子123</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑色骰子456</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白色文字Check</t>
+  </si>
+  <si>
+    <t>白色文字Start</t>
+  </si>
+  <si>
+    <t>白色文字Goal</t>
+  </si>
+  <si>
+    <t>白色文字Exit</t>
+  </si>
+  <si>
+    <t>白色文字Player</t>
+  </si>
+  <si>
+    <t>白色文字Enemy</t>
+  </si>
+  <si>
+    <t>白色文字Boss</t>
+  </si>
+  <si>
+    <t>白色文字Target</t>
+  </si>
+  <si>
+    <t>白色文字Item</t>
+  </si>
+  <si>
+    <t>白色文字Treasure</t>
+  </si>
+  <si>
+    <t>彩色文字Check</t>
+  </si>
+  <si>
+    <t>彩色文字Start</t>
+  </si>
+  <si>
+    <t>彩色文字Goal</t>
+  </si>
+  <si>
+    <t>彩色文字Exit</t>
+  </si>
+  <si>
+    <t>彩色文字Player</t>
+  </si>
+  <si>
+    <t>彩色文字Enemy</t>
+  </si>
+  <si>
+    <t>彩色文字Boss</t>
+  </si>
+  <si>
+    <t>彩色文字Target</t>
+  </si>
+  <si>
+    <t>彩色文字Item</t>
+  </si>
+  <si>
+    <t>彩色文字Treasure</t>
+  </si>
+  <si>
+    <t>白色文字New</t>
+  </si>
+  <si>
+    <t>白色文字INFO</t>
+  </si>
+  <si>
+    <t>白色文字Save</t>
+  </si>
+  <si>
+    <t>白色文字Get</t>
+  </si>
+  <si>
+    <t>白色文字Talk</t>
+  </si>
+  <si>
+    <t>白色文字Quest</t>
+  </si>
+  <si>
+    <t>白色文字Event</t>
+  </si>
+  <si>
+    <t>白色文字warp</t>
+  </si>
+  <si>
+    <t>白色文字Battle</t>
+  </si>
+  <si>
+    <t>白色文字Action</t>
+  </si>
+  <si>
+    <t>彩色文字New</t>
+  </si>
+  <si>
+    <t>彩色文字INFO</t>
+  </si>
+  <si>
+    <t>彩色文字Save</t>
+  </si>
+  <si>
+    <t>彩色文字Get</t>
+  </si>
+  <si>
+    <t>彩色文字Talk</t>
+  </si>
+  <si>
+    <t>彩色文字Quest</t>
+  </si>
+  <si>
+    <t>彩色文字Event</t>
+  </si>
+  <si>
+    <t>彩色文字warp</t>
+  </si>
+  <si>
+    <t>彩色文字Battle</t>
+  </si>
+  <si>
+    <t>彩色文字Action</t>
   </si>
 </sst>
 </file>
@@ -561,9 +1012,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:E48"/>
+  <dimension ref="A2:E183"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="2" max="2" width="23.625" customWidth="1"/>
     <col min="3" max="3" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1351,24 +1803,2319 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48">
+        <v>44</v>
+      </c>
+      <c r="B48" t="s">
+        <v>56</v>
+      </c>
+      <c r="C48">
+        <v>44</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="E48">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>45</v>
+      </c>
+      <c r="B49" t="s">
+        <v>55</v>
+      </c>
+      <c r="C49">
+        <v>45</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+      <c r="E49">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>46</v>
+      </c>
+      <c r="B50" t="s">
+        <v>57</v>
+      </c>
+      <c r="C50">
+        <v>46</v>
+      </c>
+      <c r="D50">
+        <v>0</v>
+      </c>
+      <c r="E50">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>47</v>
+      </c>
+      <c r="B51" t="s">
+        <v>58</v>
+      </c>
+      <c r="C51">
+        <v>47</v>
+      </c>
+      <c r="D51">
+        <v>0</v>
+      </c>
+      <c r="E51">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>48</v>
+      </c>
+      <c r="B52" t="s">
+        <v>59</v>
+      </c>
+      <c r="C52">
+        <v>48</v>
+      </c>
+      <c r="D52">
+        <v>0</v>
+      </c>
+      <c r="E52">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <v>49</v>
+      </c>
+      <c r="B53" t="s">
+        <v>60</v>
+      </c>
+      <c r="C53">
+        <v>49</v>
+      </c>
+      <c r="D53">
+        <v>0</v>
+      </c>
+      <c r="E53">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>50</v>
+      </c>
+      <c r="B54" t="s">
+        <v>61</v>
+      </c>
+      <c r="C54">
+        <v>50</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+      <c r="E54">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>51</v>
+      </c>
+      <c r="B55" t="s">
+        <v>62</v>
+      </c>
+      <c r="C55">
+        <v>51</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+      <c r="E55">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>52</v>
+      </c>
+      <c r="B56" t="s">
+        <v>64</v>
+      </c>
+      <c r="C56">
+        <v>52</v>
+      </c>
+      <c r="D56">
+        <v>0</v>
+      </c>
+      <c r="E56">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A57">
+        <v>53</v>
+      </c>
+      <c r="B57" t="s">
+        <v>63</v>
+      </c>
+      <c r="C57">
+        <v>53</v>
+      </c>
+      <c r="D57">
+        <v>0</v>
+      </c>
+      <c r="E57">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A58">
+        <v>54</v>
+      </c>
+      <c r="B58" t="s">
+        <v>65</v>
+      </c>
+      <c r="C58">
+        <v>54</v>
+      </c>
+      <c r="D58">
+        <v>0</v>
+      </c>
+      <c r="E58">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A59">
+        <v>55</v>
+      </c>
+      <c r="B59" t="s">
+        <v>66</v>
+      </c>
+      <c r="C59">
+        <v>55</v>
+      </c>
+      <c r="D59">
+        <v>0</v>
+      </c>
+      <c r="E59">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A60">
+        <v>56</v>
+      </c>
+      <c r="B60" t="s">
+        <v>67</v>
+      </c>
+      <c r="C60">
+        <v>56</v>
+      </c>
+      <c r="D60">
+        <v>0</v>
+      </c>
+      <c r="E60">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A61">
+        <v>57</v>
+      </c>
+      <c r="B61" t="s">
+        <v>68</v>
+      </c>
+      <c r="C61">
+        <v>57</v>
+      </c>
+      <c r="D61">
+        <v>0</v>
+      </c>
+      <c r="E61">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A62">
+        <v>58</v>
+      </c>
+      <c r="B62" t="s">
+        <v>69</v>
+      </c>
+      <c r="C62">
+        <v>58</v>
+      </c>
+      <c r="D62">
+        <v>0</v>
+      </c>
+      <c r="E62">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A63">
+        <v>59</v>
+      </c>
+      <c r="B63" t="s">
+        <v>70</v>
+      </c>
+      <c r="C63">
+        <v>59</v>
+      </c>
+      <c r="D63">
+        <v>0</v>
+      </c>
+      <c r="E63">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A64">
+        <v>60</v>
+      </c>
+      <c r="B64" t="s">
+        <v>71</v>
+      </c>
+      <c r="C64">
+        <v>60</v>
+      </c>
+      <c r="D64">
+        <v>0</v>
+      </c>
+      <c r="E64">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A65">
+        <v>61</v>
+      </c>
+      <c r="B65" t="s">
         <v>72</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C65">
+        <v>61</v>
+      </c>
+      <c r="D65">
+        <v>0</v>
+      </c>
+      <c r="E65">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A66">
+        <v>62</v>
+      </c>
+      <c r="B66" t="s">
+        <v>73</v>
+      </c>
+      <c r="C66">
+        <v>62</v>
+      </c>
+      <c r="D66">
+        <v>0</v>
+      </c>
+      <c r="E66">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A67">
+        <v>63</v>
+      </c>
+      <c r="B67" t="s">
+        <v>74</v>
+      </c>
+      <c r="C67">
+        <v>63</v>
+      </c>
+      <c r="D67">
+        <v>0</v>
+      </c>
+      <c r="E67">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A68">
+        <v>64</v>
+      </c>
+      <c r="B68" t="s">
+        <v>75</v>
+      </c>
+      <c r="C68">
+        <v>64</v>
+      </c>
+      <c r="D68">
+        <v>0</v>
+      </c>
+      <c r="E68">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A69">
+        <v>65</v>
+      </c>
+      <c r="B69" t="s">
+        <v>76</v>
+      </c>
+      <c r="C69">
+        <v>65</v>
+      </c>
+      <c r="D69">
+        <v>0</v>
+      </c>
+      <c r="E69">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A70">
+        <v>66</v>
+      </c>
+      <c r="B70" t="s">
+        <v>77</v>
+      </c>
+      <c r="C70">
+        <v>66</v>
+      </c>
+      <c r="D70">
+        <v>0</v>
+      </c>
+      <c r="E70">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A71">
+        <v>67</v>
+      </c>
+      <c r="B71" t="s">
+        <v>78</v>
+      </c>
+      <c r="C71">
+        <v>67</v>
+      </c>
+      <c r="D71">
+        <v>0</v>
+      </c>
+      <c r="E71">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A72">
+        <v>68</v>
+      </c>
+      <c r="B72" t="s">
+        <v>79</v>
+      </c>
+      <c r="C72">
+        <v>68</v>
+      </c>
+      <c r="D72">
+        <v>0</v>
+      </c>
+      <c r="E72">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A73">
+        <v>69</v>
+      </c>
+      <c r="B73" t="s">
+        <v>80</v>
+      </c>
+      <c r="C73">
+        <v>69</v>
+      </c>
+      <c r="D73">
+        <v>0</v>
+      </c>
+      <c r="E73">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A74">
+        <v>70</v>
+      </c>
+      <c r="B74" t="s">
+        <v>81</v>
+      </c>
+      <c r="C74">
+        <v>70</v>
+      </c>
+      <c r="D74">
+        <v>0</v>
+      </c>
+      <c r="E74">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A75">
+        <v>71</v>
+      </c>
+      <c r="B75" t="s">
+        <v>82</v>
+      </c>
+      <c r="C75">
+        <v>71</v>
+      </c>
+      <c r="D75">
+        <v>0</v>
+      </c>
+      <c r="E75">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A76">
+        <v>72</v>
+      </c>
+      <c r="B76" t="s">
         <v>54</v>
       </c>
-      <c r="C48">
+      <c r="C76">
         <v>72</v>
       </c>
-      <c r="D48">
-        <v>0</v>
-      </c>
-      <c r="E48">
+      <c r="D76">
+        <v>0</v>
+      </c>
+      <c r="E76">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A77">
+        <v>73</v>
+      </c>
+      <c r="B77" t="s">
+        <v>85</v>
+      </c>
+      <c r="C77">
+        <v>73</v>
+      </c>
+      <c r="D77">
+        <v>0</v>
+      </c>
+      <c r="E77">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A78">
+        <v>74</v>
+      </c>
+      <c r="B78" t="s">
+        <v>83</v>
+      </c>
+      <c r="C78">
+        <v>74</v>
+      </c>
+      <c r="D78">
+        <v>0</v>
+      </c>
+      <c r="E78">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A79">
+        <v>75</v>
+      </c>
+      <c r="B79" t="s">
+        <v>84</v>
+      </c>
+      <c r="C79">
+        <v>75</v>
+      </c>
+      <c r="D79">
+        <v>0</v>
+      </c>
+      <c r="E79">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A80">
+        <v>76</v>
+      </c>
+      <c r="B80" t="s">
+        <v>86</v>
+      </c>
+      <c r="C80">
+        <v>76</v>
+      </c>
+      <c r="D80">
+        <v>0</v>
+      </c>
+      <c r="E80">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A81">
+        <v>77</v>
+      </c>
+      <c r="B81" t="s">
+        <v>87</v>
+      </c>
+      <c r="C81">
+        <v>77</v>
+      </c>
+      <c r="D81">
+        <v>0</v>
+      </c>
+      <c r="E81">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A82">
+        <v>78</v>
+      </c>
+      <c r="B82" t="s">
+        <v>88</v>
+      </c>
+      <c r="C82">
+        <v>78</v>
+      </c>
+      <c r="D82">
+        <v>0</v>
+      </c>
+      <c r="E82">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A83">
+        <v>79</v>
+      </c>
+      <c r="B83" t="s">
+        <v>89</v>
+      </c>
+      <c r="C83">
+        <v>79</v>
+      </c>
+      <c r="D83">
+        <v>0</v>
+      </c>
+      <c r="E83">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A84">
+        <v>80</v>
+      </c>
+      <c r="B84" t="s">
+        <v>90</v>
+      </c>
+      <c r="C84">
+        <v>80</v>
+      </c>
+      <c r="D84">
+        <v>0</v>
+      </c>
+      <c r="E84">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A85">
+        <v>81</v>
+      </c>
+      <c r="B85" t="s">
+        <v>91</v>
+      </c>
+      <c r="C85">
+        <v>81</v>
+      </c>
+      <c r="D85">
+        <v>0</v>
+      </c>
+      <c r="E85">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A86">
+        <v>82</v>
+      </c>
+      <c r="B86" t="s">
+        <v>92</v>
+      </c>
+      <c r="C86">
+        <v>82</v>
+      </c>
+      <c r="D86">
+        <v>0</v>
+      </c>
+      <c r="E86">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A87">
+        <v>83</v>
+      </c>
+      <c r="B87" t="s">
+        <v>93</v>
+      </c>
+      <c r="C87">
+        <v>83</v>
+      </c>
+      <c r="D87">
+        <v>0</v>
+      </c>
+      <c r="E87">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A88">
+        <v>84</v>
+      </c>
+      <c r="B88" t="s">
+        <v>94</v>
+      </c>
+      <c r="C88">
+        <v>84</v>
+      </c>
+      <c r="D88">
+        <v>0</v>
+      </c>
+      <c r="E88">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A89">
+        <v>85</v>
+      </c>
+      <c r="B89" t="s">
+        <v>95</v>
+      </c>
+      <c r="C89">
+        <v>85</v>
+      </c>
+      <c r="D89">
+        <v>0</v>
+      </c>
+      <c r="E89">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A90">
+        <v>86</v>
+      </c>
+      <c r="B90" t="s">
+        <v>96</v>
+      </c>
+      <c r="C90">
+        <v>86</v>
+      </c>
+      <c r="D90">
+        <v>0</v>
+      </c>
+      <c r="E90">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A91">
+        <v>87</v>
+      </c>
+      <c r="B91" t="s">
+        <v>97</v>
+      </c>
+      <c r="C91">
+        <v>87</v>
+      </c>
+      <c r="D91">
+        <v>0</v>
+      </c>
+      <c r="E91">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A92">
+        <v>88</v>
+      </c>
+      <c r="B92" t="s">
+        <v>98</v>
+      </c>
+      <c r="C92">
+        <v>88</v>
+      </c>
+      <c r="D92">
+        <v>0</v>
+      </c>
+      <c r="E92">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A93">
+        <v>89</v>
+      </c>
+      <c r="B93" t="s">
+        <v>99</v>
+      </c>
+      <c r="C93">
+        <v>89</v>
+      </c>
+      <c r="D93">
+        <v>0</v>
+      </c>
+      <c r="E93">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A94">
+        <v>90</v>
+      </c>
+      <c r="B94" t="s">
+        <v>100</v>
+      </c>
+      <c r="C94">
+        <v>90</v>
+      </c>
+      <c r="D94">
+        <v>0</v>
+      </c>
+      <c r="E94">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A95">
+        <v>91</v>
+      </c>
+      <c r="B95" t="s">
+        <v>101</v>
+      </c>
+      <c r="C95">
+        <v>91</v>
+      </c>
+      <c r="D95">
+        <v>0</v>
+      </c>
+      <c r="E95">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A96">
+        <v>92</v>
+      </c>
+      <c r="B96" t="s">
+        <v>102</v>
+      </c>
+      <c r="C96">
+        <v>92</v>
+      </c>
+      <c r="D96">
+        <v>0</v>
+      </c>
+      <c r="E96">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A97">
+        <v>93</v>
+      </c>
+      <c r="B97" t="s">
+        <v>103</v>
+      </c>
+      <c r="C97">
+        <v>93</v>
+      </c>
+      <c r="D97">
+        <v>0</v>
+      </c>
+      <c r="E97">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A98">
+        <v>94</v>
+      </c>
+      <c r="B98" t="s">
+        <v>104</v>
+      </c>
+      <c r="C98">
+        <v>94</v>
+      </c>
+      <c r="D98">
+        <v>0</v>
+      </c>
+      <c r="E98">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A99">
+        <v>95</v>
+      </c>
+      <c r="B99" t="s">
+        <v>105</v>
+      </c>
+      <c r="C99">
+        <v>95</v>
+      </c>
+      <c r="D99">
+        <v>0</v>
+      </c>
+      <c r="E99">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A100">
+        <v>96</v>
+      </c>
+      <c r="B100" t="s">
+        <v>106</v>
+      </c>
+      <c r="C100">
+        <v>96</v>
+      </c>
+      <c r="D100">
+        <v>0</v>
+      </c>
+      <c r="E100">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A101">
+        <v>97</v>
+      </c>
+      <c r="B101" t="s">
+        <v>107</v>
+      </c>
+      <c r="C101">
+        <v>97</v>
+      </c>
+      <c r="D101">
+        <v>0</v>
+      </c>
+      <c r="E101">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A102">
+        <v>98</v>
+      </c>
+      <c r="B102" t="s">
+        <v>108</v>
+      </c>
+      <c r="C102">
+        <v>98</v>
+      </c>
+      <c r="D102">
+        <v>0</v>
+      </c>
+      <c r="E102">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A103">
+        <v>99</v>
+      </c>
+      <c r="B103" t="s">
+        <v>109</v>
+      </c>
+      <c r="C103">
+        <v>99</v>
+      </c>
+      <c r="D103">
+        <v>0</v>
+      </c>
+      <c r="E103">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A104">
+        <v>100</v>
+      </c>
+      <c r="B104">
+        <v>0</v>
+      </c>
+      <c r="C104">
+        <v>100</v>
+      </c>
+      <c r="D104">
+        <v>0</v>
+      </c>
+      <c r="E104">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A105">
+        <v>101</v>
+      </c>
+      <c r="B105">
+        <v>1</v>
+      </c>
+      <c r="C105">
+        <v>101</v>
+      </c>
+      <c r="D105">
+        <v>0</v>
+      </c>
+      <c r="E105">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A106">
+        <v>102</v>
+      </c>
+      <c r="B106">
+        <v>2</v>
+      </c>
+      <c r="C106">
+        <v>102</v>
+      </c>
+      <c r="D106">
+        <v>0</v>
+      </c>
+      <c r="E106">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A107">
+        <v>103</v>
+      </c>
+      <c r="B107">
+        <v>3</v>
+      </c>
+      <c r="C107">
+        <v>103</v>
+      </c>
+      <c r="D107">
+        <v>0</v>
+      </c>
+      <c r="E107">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A108">
+        <v>104</v>
+      </c>
+      <c r="B108">
+        <v>4</v>
+      </c>
+      <c r="C108">
+        <v>104</v>
+      </c>
+      <c r="D108">
+        <v>0</v>
+      </c>
+      <c r="E108">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A109">
+        <v>105</v>
+      </c>
+      <c r="B109">
+        <v>5</v>
+      </c>
+      <c r="C109">
+        <v>105</v>
+      </c>
+      <c r="D109">
+        <v>0</v>
+      </c>
+      <c r="E109">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A110">
+        <v>106</v>
+      </c>
+      <c r="B110">
+        <v>6</v>
+      </c>
+      <c r="C110">
+        <v>106</v>
+      </c>
+      <c r="D110">
+        <v>0</v>
+      </c>
+      <c r="E110">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A111">
+        <v>107</v>
+      </c>
+      <c r="B111">
+        <v>7</v>
+      </c>
+      <c r="C111">
+        <v>107</v>
+      </c>
+      <c r="D111">
+        <v>0</v>
+      </c>
+      <c r="E111">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A112">
+        <v>108</v>
+      </c>
+      <c r="B112">
+        <v>8</v>
+      </c>
+      <c r="C112">
+        <v>108</v>
+      </c>
+      <c r="D112">
+        <v>0</v>
+      </c>
+      <c r="E112">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A113">
+        <v>109</v>
+      </c>
+      <c r="B113">
+        <v>9</v>
+      </c>
+      <c r="C113">
+        <v>109</v>
+      </c>
+      <c r="D113">
+        <v>0</v>
+      </c>
+      <c r="E113">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A114">
+        <v>110</v>
+      </c>
+      <c r="B114" t="s">
+        <v>110</v>
+      </c>
+      <c r="C114">
+        <v>110</v>
+      </c>
+      <c r="D114">
+        <v>0</v>
+      </c>
+      <c r="E114">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A115">
+        <v>111</v>
+      </c>
+      <c r="B115" t="s">
+        <v>111</v>
+      </c>
+      <c r="C115">
+        <v>111</v>
+      </c>
+      <c r="D115">
+        <v>0</v>
+      </c>
+      <c r="E115">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A116">
+        <v>112</v>
+      </c>
+      <c r="B116" t="s">
+        <v>112</v>
+      </c>
+      <c r="C116">
+        <v>112</v>
+      </c>
+      <c r="D116">
+        <v>0</v>
+      </c>
+      <c r="E116">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A117">
+        <v>113</v>
+      </c>
+      <c r="B117" t="s">
+        <v>113</v>
+      </c>
+      <c r="C117">
+        <v>113</v>
+      </c>
+      <c r="D117">
+        <v>0</v>
+      </c>
+      <c r="E117">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A118">
+        <v>114</v>
+      </c>
+      <c r="B118" t="s">
+        <v>114</v>
+      </c>
+      <c r="C118">
+        <v>114</v>
+      </c>
+      <c r="D118">
+        <v>0</v>
+      </c>
+      <c r="E118">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A119">
+        <v>115</v>
+      </c>
+      <c r="B119" t="s">
+        <v>115</v>
+      </c>
+      <c r="C119">
+        <v>115</v>
+      </c>
+      <c r="D119">
+        <v>0</v>
+      </c>
+      <c r="E119">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A120">
+        <v>116</v>
+      </c>
+      <c r="B120" t="s">
+        <v>116</v>
+      </c>
+      <c r="C120">
+        <v>116</v>
+      </c>
+      <c r="D120">
+        <v>0</v>
+      </c>
+      <c r="E120">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A121">
+        <v>117</v>
+      </c>
+      <c r="B121" t="s">
+        <v>117</v>
+      </c>
+      <c r="C121">
+        <v>117</v>
+      </c>
+      <c r="D121">
+        <v>0</v>
+      </c>
+      <c r="E121">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A122">
+        <v>118</v>
+      </c>
+      <c r="B122" t="s">
+        <v>119</v>
+      </c>
+      <c r="C122">
+        <v>118</v>
+      </c>
+      <c r="D122">
+        <v>0</v>
+      </c>
+      <c r="E122">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A123">
+        <v>119</v>
+      </c>
+      <c r="B123" t="s">
+        <v>118</v>
+      </c>
+      <c r="C123">
+        <v>119</v>
+      </c>
+      <c r="D123">
+        <v>0</v>
+      </c>
+      <c r="E123">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A124">
+        <v>120</v>
+      </c>
+      <c r="B124" t="s">
+        <v>120</v>
+      </c>
+      <c r="C124">
+        <v>120</v>
+      </c>
+      <c r="D124">
+        <v>0</v>
+      </c>
+      <c r="E124">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A125">
+        <v>121</v>
+      </c>
+      <c r="B125" t="s">
+        <v>121</v>
+      </c>
+      <c r="C125">
+        <v>121</v>
+      </c>
+      <c r="D125">
+        <v>0</v>
+      </c>
+      <c r="E125">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A126">
+        <v>122</v>
+      </c>
+      <c r="B126" t="s">
+        <v>122</v>
+      </c>
+      <c r="C126">
+        <v>122</v>
+      </c>
+      <c r="D126">
+        <v>0</v>
+      </c>
+      <c r="E126">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A127">
+        <v>123</v>
+      </c>
+      <c r="B127" t="s">
+        <v>123</v>
+      </c>
+      <c r="C127">
+        <v>123</v>
+      </c>
+      <c r="D127">
+        <v>0</v>
+      </c>
+      <c r="E127">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A128">
+        <v>124</v>
+      </c>
+      <c r="B128" t="s">
+        <v>124</v>
+      </c>
+      <c r="C128">
+        <v>124</v>
+      </c>
+      <c r="D128">
+        <v>0</v>
+      </c>
+      <c r="E128">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A129">
+        <v>125</v>
+      </c>
+      <c r="B129" t="s">
+        <v>125</v>
+      </c>
+      <c r="C129">
+        <v>125</v>
+      </c>
+      <c r="D129">
+        <v>0</v>
+      </c>
+      <c r="E129">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A130">
+        <v>126</v>
+      </c>
+      <c r="B130" t="s">
+        <v>126</v>
+      </c>
+      <c r="C130">
+        <v>126</v>
+      </c>
+      <c r="D130">
+        <v>0</v>
+      </c>
+      <c r="E130">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A131">
+        <v>127</v>
+      </c>
+      <c r="B131" t="s">
+        <v>127</v>
+      </c>
+      <c r="C131">
+        <v>127</v>
+      </c>
+      <c r="D131">
+        <v>0</v>
+      </c>
+      <c r="E131">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A132">
+        <v>128</v>
+      </c>
+      <c r="B132" t="s">
+        <v>128</v>
+      </c>
+      <c r="C132">
+        <v>128</v>
+      </c>
+      <c r="D132">
+        <v>0</v>
+      </c>
+      <c r="E132">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A133">
+        <v>129</v>
+      </c>
+      <c r="B133" t="s">
+        <v>129</v>
+      </c>
+      <c r="C133">
+        <v>129</v>
+      </c>
+      <c r="D133">
+        <v>0</v>
+      </c>
+      <c r="E133">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A134">
+        <v>130</v>
+      </c>
+      <c r="B134" t="s">
+        <v>130</v>
+      </c>
+      <c r="C134">
+        <v>130</v>
+      </c>
+      <c r="D134">
+        <v>0</v>
+      </c>
+      <c r="E134">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A135">
+        <v>131</v>
+      </c>
+      <c r="B135" t="s">
+        <v>131</v>
+      </c>
+      <c r="C135">
+        <v>131</v>
+      </c>
+      <c r="D135">
+        <v>0</v>
+      </c>
+      <c r="E135">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A136">
+        <v>132</v>
+      </c>
+      <c r="B136" t="s">
+        <v>132</v>
+      </c>
+      <c r="C136">
+        <v>132</v>
+      </c>
+      <c r="D136">
+        <v>0</v>
+      </c>
+      <c r="E136">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A137">
+        <v>133</v>
+      </c>
+      <c r="B137" t="s">
+        <v>133</v>
+      </c>
+      <c r="C137">
+        <v>133</v>
+      </c>
+      <c r="D137">
+        <v>0</v>
+      </c>
+      <c r="E137">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A138">
+        <v>134</v>
+      </c>
+      <c r="B138" t="s">
+        <v>134</v>
+      </c>
+      <c r="C138">
+        <v>134</v>
+      </c>
+      <c r="D138">
+        <v>0</v>
+      </c>
+      <c r="E138">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A139">
+        <v>135</v>
+      </c>
+      <c r="B139" t="s">
+        <v>135</v>
+      </c>
+      <c r="C139">
+        <v>135</v>
+      </c>
+      <c r="D139">
+        <v>0</v>
+      </c>
+      <c r="E139">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A140">
+        <v>136</v>
+      </c>
+      <c r="B140" t="s">
+        <v>136</v>
+      </c>
+      <c r="C140">
+        <v>136</v>
+      </c>
+      <c r="D140">
+        <v>0</v>
+      </c>
+      <c r="E140">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A141">
+        <v>137</v>
+      </c>
+      <c r="B141" t="s">
+        <v>137</v>
+      </c>
+      <c r="C141">
+        <v>137</v>
+      </c>
+      <c r="D141">
+        <v>0</v>
+      </c>
+      <c r="E141">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A142">
+        <v>138</v>
+      </c>
+      <c r="B142" t="s">
+        <v>138</v>
+      </c>
+      <c r="C142">
+        <v>138</v>
+      </c>
+      <c r="D142">
+        <v>0</v>
+      </c>
+      <c r="E142">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A143">
+        <v>139</v>
+      </c>
+      <c r="B143" t="s">
+        <v>139</v>
+      </c>
+      <c r="C143">
+        <v>139</v>
+      </c>
+      <c r="D143">
+        <v>0</v>
+      </c>
+      <c r="E143">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A144">
+        <v>140</v>
+      </c>
+      <c r="B144" t="s">
+        <v>140</v>
+      </c>
+      <c r="C144">
+        <v>140</v>
+      </c>
+      <c r="D144">
+        <v>0</v>
+      </c>
+      <c r="E144">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A145">
+        <v>141</v>
+      </c>
+      <c r="B145" t="s">
+        <v>141</v>
+      </c>
+      <c r="C145">
+        <v>141</v>
+      </c>
+      <c r="D145">
+        <v>0</v>
+      </c>
+      <c r="E145">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A146">
+        <v>142</v>
+      </c>
+      <c r="B146" t="s">
+        <v>142</v>
+      </c>
+      <c r="C146">
+        <v>142</v>
+      </c>
+      <c r="D146">
+        <v>0</v>
+      </c>
+      <c r="E146">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A147">
+        <v>143</v>
+      </c>
+      <c r="B147" t="s">
+        <v>143</v>
+      </c>
+      <c r="C147">
+        <v>143</v>
+      </c>
+      <c r="D147">
+        <v>0</v>
+      </c>
+      <c r="E147">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A148">
+        <v>144</v>
+      </c>
+      <c r="B148" t="s">
+        <v>144</v>
+      </c>
+      <c r="C148">
+        <v>144</v>
+      </c>
+      <c r="D148">
+        <v>0</v>
+      </c>
+      <c r="E148">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A149">
+        <v>145</v>
+      </c>
+      <c r="B149" t="s">
+        <v>145</v>
+      </c>
+      <c r="C149">
+        <v>145</v>
+      </c>
+      <c r="D149">
+        <v>0</v>
+      </c>
+      <c r="E149">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A150">
+        <v>146</v>
+      </c>
+      <c r="B150" t="s">
+        <v>146</v>
+      </c>
+      <c r="C150">
+        <v>146</v>
+      </c>
+      <c r="D150">
+        <v>0</v>
+      </c>
+      <c r="E150">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A151">
+        <v>147</v>
+      </c>
+      <c r="B151" t="s">
+        <v>147</v>
+      </c>
+      <c r="C151">
+        <v>147</v>
+      </c>
+      <c r="D151">
+        <v>0</v>
+      </c>
+      <c r="E151">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A152">
+        <v>148</v>
+      </c>
+      <c r="B152" t="s">
+        <v>148</v>
+      </c>
+      <c r="C152">
+        <v>148</v>
+      </c>
+      <c r="D152">
+        <v>0</v>
+      </c>
+      <c r="E152">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A153">
+        <v>149</v>
+      </c>
+      <c r="B153" t="s">
+        <v>149</v>
+      </c>
+      <c r="C153">
+        <v>149</v>
+      </c>
+      <c r="D153">
+        <v>0</v>
+      </c>
+      <c r="E153">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A154">
+        <v>150</v>
+      </c>
+      <c r="B154" t="s">
+        <v>150</v>
+      </c>
+      <c r="C154">
+        <v>150</v>
+      </c>
+      <c r="D154">
+        <v>0</v>
+      </c>
+      <c r="E154">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A155">
+        <v>151</v>
+      </c>
+      <c r="B155" t="s">
+        <v>151</v>
+      </c>
+      <c r="C155">
+        <v>151</v>
+      </c>
+      <c r="D155">
+        <v>0</v>
+      </c>
+      <c r="E155">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A156">
+        <v>152</v>
+      </c>
+      <c r="B156" t="s">
+        <v>152</v>
+      </c>
+      <c r="C156">
+        <v>152</v>
+      </c>
+      <c r="D156">
+        <v>0</v>
+      </c>
+      <c r="E156">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A157">
+        <v>153</v>
+      </c>
+      <c r="B157" t="s">
+        <v>153</v>
+      </c>
+      <c r="C157">
+        <v>153</v>
+      </c>
+      <c r="D157">
+        <v>0</v>
+      </c>
+      <c r="E157">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A158">
+        <v>154</v>
+      </c>
+      <c r="B158" t="s">
+        <v>154</v>
+      </c>
+      <c r="C158">
+        <v>154</v>
+      </c>
+      <c r="D158">
+        <v>0</v>
+      </c>
+      <c r="E158">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A159">
+        <v>155</v>
+      </c>
+      <c r="B159" t="s">
+        <v>155</v>
+      </c>
+      <c r="C159">
+        <v>155</v>
+      </c>
+      <c r="D159">
+        <v>0</v>
+      </c>
+      <c r="E159">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A160">
+        <v>156</v>
+      </c>
+      <c r="B160" t="s">
+        <v>156</v>
+      </c>
+      <c r="C160">
+        <v>156</v>
+      </c>
+      <c r="D160">
+        <v>0</v>
+      </c>
+      <c r="E160">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A161">
+        <v>157</v>
+      </c>
+      <c r="B161" t="s">
+        <v>157</v>
+      </c>
+      <c r="C161">
+        <v>157</v>
+      </c>
+      <c r="D161">
+        <v>0</v>
+      </c>
+      <c r="E161">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A162">
+        <v>158</v>
+      </c>
+      <c r="B162" t="s">
+        <v>158</v>
+      </c>
+      <c r="C162">
+        <v>158</v>
+      </c>
+      <c r="D162">
+        <v>0</v>
+      </c>
+      <c r="E162">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A163">
+        <v>159</v>
+      </c>
+      <c r="B163" t="s">
+        <v>159</v>
+      </c>
+      <c r="C163">
+        <v>159</v>
+      </c>
+      <c r="D163">
+        <v>0</v>
+      </c>
+      <c r="E163">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A164">
+        <v>160</v>
+      </c>
+      <c r="B164" t="s">
+        <v>160</v>
+      </c>
+      <c r="C164">
+        <v>160</v>
+      </c>
+      <c r="D164">
+        <v>0</v>
+      </c>
+      <c r="E164">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A165">
+        <v>161</v>
+      </c>
+      <c r="B165" t="s">
+        <v>161</v>
+      </c>
+      <c r="C165">
+        <v>161</v>
+      </c>
+      <c r="D165">
+        <v>0</v>
+      </c>
+      <c r="E165">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A166">
+        <v>162</v>
+      </c>
+      <c r="B166" t="s">
+        <v>162</v>
+      </c>
+      <c r="C166">
+        <v>162</v>
+      </c>
+      <c r="D166">
+        <v>0</v>
+      </c>
+      <c r="E166">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A167">
+        <v>163</v>
+      </c>
+      <c r="B167" t="s">
+        <v>163</v>
+      </c>
+      <c r="C167">
+        <v>163</v>
+      </c>
+      <c r="D167">
+        <v>0</v>
+      </c>
+      <c r="E167">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A168">
+        <v>164</v>
+      </c>
+      <c r="B168" t="s">
+        <v>164</v>
+      </c>
+      <c r="C168">
+        <v>164</v>
+      </c>
+      <c r="D168">
+        <v>0</v>
+      </c>
+      <c r="E168">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A169">
+        <v>165</v>
+      </c>
+      <c r="B169" t="s">
+        <v>165</v>
+      </c>
+      <c r="C169">
+        <v>165</v>
+      </c>
+      <c r="D169">
+        <v>0</v>
+      </c>
+      <c r="E169">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A170">
+        <v>166</v>
+      </c>
+      <c r="B170" t="s">
+        <v>166</v>
+      </c>
+      <c r="C170">
+        <v>166</v>
+      </c>
+      <c r="D170">
+        <v>0</v>
+      </c>
+      <c r="E170">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A171">
+        <v>167</v>
+      </c>
+      <c r="B171" t="s">
+        <v>167</v>
+      </c>
+      <c r="C171">
+        <v>167</v>
+      </c>
+      <c r="D171">
+        <v>0</v>
+      </c>
+      <c r="E171">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A172">
+        <v>168</v>
+      </c>
+      <c r="B172" t="s">
+        <v>168</v>
+      </c>
+      <c r="C172">
+        <v>168</v>
+      </c>
+      <c r="D172">
+        <v>0</v>
+      </c>
+      <c r="E172">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A173">
+        <v>169</v>
+      </c>
+      <c r="B173" t="s">
+        <v>169</v>
+      </c>
+      <c r="C173">
+        <v>169</v>
+      </c>
+      <c r="D173">
+        <v>0</v>
+      </c>
+      <c r="E173">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A174">
+        <v>170</v>
+      </c>
+      <c r="B174" t="s">
+        <v>170</v>
+      </c>
+      <c r="C174">
+        <v>170</v>
+      </c>
+      <c r="D174">
+        <v>0</v>
+      </c>
+      <c r="E174">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A175">
+        <v>171</v>
+      </c>
+      <c r="B175" t="s">
+        <v>171</v>
+      </c>
+      <c r="C175">
+        <v>171</v>
+      </c>
+      <c r="D175">
+        <v>0</v>
+      </c>
+      <c r="E175">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A176">
+        <v>172</v>
+      </c>
+      <c r="B176" t="s">
+        <v>172</v>
+      </c>
+      <c r="C176">
+        <v>172</v>
+      </c>
+      <c r="D176">
+        <v>0</v>
+      </c>
+      <c r="E176">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A177">
+        <v>173</v>
+      </c>
+      <c r="B177" t="s">
+        <v>173</v>
+      </c>
+      <c r="C177">
+        <v>173</v>
+      </c>
+      <c r="D177">
+        <v>0</v>
+      </c>
+      <c r="E177">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A178">
+        <v>174</v>
+      </c>
+      <c r="B178" t="s">
+        <v>174</v>
+      </c>
+      <c r="C178">
+        <v>174</v>
+      </c>
+      <c r="D178">
+        <v>0</v>
+      </c>
+      <c r="E178">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A179">
+        <v>175</v>
+      </c>
+      <c r="B179" t="s">
+        <v>175</v>
+      </c>
+      <c r="C179">
+        <v>175</v>
+      </c>
+      <c r="D179">
+        <v>0</v>
+      </c>
+      <c r="E179">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A180">
+        <v>176</v>
+      </c>
+      <c r="B180" t="s">
+        <v>176</v>
+      </c>
+      <c r="C180">
+        <v>176</v>
+      </c>
+      <c r="D180">
+        <v>0</v>
+      </c>
+      <c r="E180">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A181">
+        <v>177</v>
+      </c>
+      <c r="B181" t="s">
+        <v>177</v>
+      </c>
+      <c r="C181">
+        <v>177</v>
+      </c>
+      <c r="D181">
+        <v>0</v>
+      </c>
+      <c r="E181">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A182">
+        <v>178</v>
+      </c>
+      <c r="B182" t="s">
+        <v>178</v>
+      </c>
+      <c r="C182">
+        <v>178</v>
+      </c>
+      <c r="D182">
+        <v>0</v>
+      </c>
+      <c r="E182">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A183">
+        <v>179</v>
+      </c>
+      <c r="B183" t="s">
+        <v>179</v>
+      </c>
+      <c r="C183">
+        <v>179</v>
+      </c>
+      <c r="D183">
+        <v>0</v>
+      </c>
+      <c r="E183">
         <v>60</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Datas/EmoteData.xlsx
+++ b/Datas/EmoteData.xlsx
@@ -51,43 +51,627 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>生气</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑线</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>汗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爱心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爱心破碎</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>感叹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>疑问</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>强烈疑问</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>喊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大星星</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>流星</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>脸红</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>亲吻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>红花</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小花</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>彩带</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>箭靶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>亮灯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>晕</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>降水</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>撒汗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>骷髅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爆气</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>落石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>星星眼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>闭眼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>痴汉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恐惧</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生气</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>眼睛放光</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火焰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰冻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>开裂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>血</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>加载</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>倒计时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>法阵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多角星</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>四芒星</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>咬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文字</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>曲谱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数字</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计算符号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多云</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>太阳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷雨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大雨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雪人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>月亮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>面包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>肉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蘑菇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>苹果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蛋糕</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>茶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>啤酒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>信</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>炸弹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>锤子砸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>按钮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>钻石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一箱子金币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>礼物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奖杯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奖牌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>王冠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恶魔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幽灵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>便便</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拳头</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>剪刀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>向上箭头</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>下降箭头</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑桃</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>红心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>梅花</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>方片</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>男性标志</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>女性标志</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>o标志</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>x标志</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>三角</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>矩形</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>箭头上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>箭头下</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>箭头左</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>箭头右</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>箭头左上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>箭头右上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>箭头左下</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>箭头右下</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>窄三角三</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宽三角三</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白色三角上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白色三角下</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白色三角左</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白色三角右</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白色三角左上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白色三角右上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白色三角左下</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白色三角右下</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白色骰子123</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白色骰子456</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>红色三角上</t>
+  </si>
+  <si>
+    <t>红色三角下</t>
+  </si>
+  <si>
+    <t>红色三角左</t>
+  </si>
+  <si>
+    <t>红色三角右</t>
+  </si>
+  <si>
+    <t>红色三角左上</t>
+  </si>
+  <si>
+    <t>红色三角右上</t>
+  </si>
+  <si>
+    <t>红色三角左下</t>
+  </si>
+  <si>
+    <t>红色三角右下</t>
+  </si>
+  <si>
+    <t>黑色骰子123</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑色骰子456</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白色文字Check</t>
+  </si>
+  <si>
+    <t>白色文字Start</t>
+  </si>
+  <si>
+    <t>白色文字Goal</t>
+  </si>
+  <si>
+    <t>白色文字Exit</t>
+  </si>
+  <si>
+    <t>白色文字Player</t>
+  </si>
+  <si>
+    <t>白色文字Enemy</t>
+  </si>
+  <si>
+    <t>白色文字Boss</t>
+  </si>
+  <si>
+    <t>白色文字Target</t>
+  </si>
+  <si>
+    <t>白色文字Item</t>
+  </si>
+  <si>
+    <t>白色文字Treasure</t>
+  </si>
+  <si>
+    <t>彩色文字Check</t>
+  </si>
+  <si>
+    <t>彩色文字Start</t>
+  </si>
+  <si>
+    <t>彩色文字Goal</t>
+  </si>
+  <si>
+    <t>彩色文字Exit</t>
+  </si>
+  <si>
+    <t>彩色文字Player</t>
+  </si>
+  <si>
+    <t>彩色文字Enemy</t>
+  </si>
+  <si>
+    <t>彩色文字Boss</t>
+  </si>
+  <si>
+    <t>彩色文字Target</t>
+  </si>
+  <si>
+    <t>彩色文字Item</t>
+  </si>
+  <si>
+    <t>彩色文字Treasure</t>
+  </si>
+  <si>
+    <t>白色文字New</t>
+  </si>
+  <si>
+    <t>白色文字INFO</t>
+  </si>
+  <si>
+    <t>白色文字Save</t>
+  </si>
+  <si>
+    <t>白色文字Get</t>
+  </si>
+  <si>
+    <t>白色文字Talk</t>
+  </si>
+  <si>
+    <t>白色文字Quest</t>
+  </si>
+  <si>
+    <t>白色文字Event</t>
+  </si>
+  <si>
+    <t>白色文字warp</t>
+  </si>
+  <si>
+    <t>白色文字Battle</t>
+  </si>
+  <si>
+    <t>白色文字Action</t>
+  </si>
+  <si>
+    <t>彩色文字New</t>
+  </si>
+  <si>
+    <t>彩色文字INFO</t>
+  </si>
+  <si>
+    <t>彩色文字Save</t>
+  </si>
+  <si>
+    <t>彩色文字Get</t>
+  </si>
+  <si>
+    <t>彩色文字Talk</t>
+  </si>
+  <si>
+    <t>彩色文字Quest</t>
+  </si>
+  <si>
+    <t>彩色文字Event</t>
+  </si>
+  <si>
+    <t>彩色文字warp</t>
+  </si>
+  <si>
+    <t>彩色文字Battle</t>
+  </si>
+  <si>
+    <t>彩色文字Action</t>
+  </si>
+  <si>
+    <t>流口水</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>睡眠</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>生气</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黑线</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>汗</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>爱心</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>爱心破碎</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>感叹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>疑问</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>强烈疑问</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>喊</t>
+    <t>天使</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小星星</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>眨眼</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -95,199 +679,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>小星星</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>大星星</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>流星</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>脸红</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>亲吻</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>红花</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>小花</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>彩带</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>箭靶</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>亮灯</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>晕</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>雾</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>降水</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>撒汗</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>骷髅</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>爆气</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>落石</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>星星眼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>眨眼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>闭眼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>痴汉</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>流口水</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>恐惧</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>生气</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>眼睛放光</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>火焰</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>冰冻</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>开裂</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>血</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>加载</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>战斗</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Y</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>倒计时</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>法阵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>多角星</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>四芒星</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>咬</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>文字</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>曲谱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>数字</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计算符号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>多云</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>太阳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>雷雨</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>大雨</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>雪人</t>
+    <t>金币</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -295,399 +687,8 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>月亮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>面包</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>肉</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>鱼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>蘑菇</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>苹果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>蛋糕</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>茶</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>啤酒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>信</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>翻书</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>炸弹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>锤子砸</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>按钮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>钻石</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一箱子金币</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>金币</t>
-  </si>
-  <si>
-    <t>礼物</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>奖杯</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>奖牌</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>王冠</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>小鸡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>天使</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>恶魔</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>幽灵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>便便</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>拳头</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>剪刀</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>布</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>向上箭头</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>下降箭头</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黑桃</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>红心</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>梅花</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>方片</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>男性标志</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>女性标志</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>o标志</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>x标志</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>三角</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>矩形</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>箭头上</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>箭头下</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>箭头左</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>箭头右</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>箭头左上</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>箭头右上</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>箭头左下</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>箭头右下</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>窄三角三</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>宽三角三</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>白色三角上</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>白色三角下</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>白色三角左</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>白色三角右</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>白色三角左上</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>白色三角右上</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>白色三角左下</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>白色三角右下</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>白色骰子123</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>白色骰子456</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>红色三角上</t>
-  </si>
-  <si>
-    <t>红色三角下</t>
-  </si>
-  <si>
-    <t>红色三角左</t>
-  </si>
-  <si>
-    <t>红色三角右</t>
-  </si>
-  <si>
-    <t>红色三角左上</t>
-  </si>
-  <si>
-    <t>红色三角右上</t>
-  </si>
-  <si>
-    <t>红色三角左下</t>
-  </si>
-  <si>
-    <t>红色三角右下</t>
-  </si>
-  <si>
-    <t>黑色骰子123</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黑色骰子456</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>白色文字Check</t>
-  </si>
-  <si>
-    <t>白色文字Start</t>
-  </si>
-  <si>
-    <t>白色文字Goal</t>
-  </si>
-  <si>
-    <t>白色文字Exit</t>
-  </si>
-  <si>
-    <t>白色文字Player</t>
-  </si>
-  <si>
-    <t>白色文字Enemy</t>
-  </si>
-  <si>
-    <t>白色文字Boss</t>
-  </si>
-  <si>
-    <t>白色文字Target</t>
-  </si>
-  <si>
-    <t>白色文字Item</t>
-  </si>
-  <si>
-    <t>白色文字Treasure</t>
-  </si>
-  <si>
-    <t>彩色文字Check</t>
-  </si>
-  <si>
-    <t>彩色文字Start</t>
-  </si>
-  <si>
-    <t>彩色文字Goal</t>
-  </si>
-  <si>
-    <t>彩色文字Exit</t>
-  </si>
-  <si>
-    <t>彩色文字Player</t>
-  </si>
-  <si>
-    <t>彩色文字Enemy</t>
-  </si>
-  <si>
-    <t>彩色文字Boss</t>
-  </si>
-  <si>
-    <t>彩色文字Target</t>
-  </si>
-  <si>
-    <t>彩色文字Item</t>
-  </si>
-  <si>
-    <t>彩色文字Treasure</t>
-  </si>
-  <si>
-    <t>白色文字New</t>
-  </si>
-  <si>
-    <t>白色文字INFO</t>
-  </si>
-  <si>
-    <t>白色文字Save</t>
-  </si>
-  <si>
-    <t>白色文字Get</t>
-  </si>
-  <si>
-    <t>白色文字Talk</t>
-  </si>
-  <si>
-    <t>白色文字Quest</t>
-  </si>
-  <si>
-    <t>白色文字Event</t>
-  </si>
-  <si>
-    <t>白色文字warp</t>
-  </si>
-  <si>
-    <t>白色文字Battle</t>
-  </si>
-  <si>
-    <t>白色文字Action</t>
-  </si>
-  <si>
-    <t>彩色文字New</t>
-  </si>
-  <si>
-    <t>彩色文字INFO</t>
-  </si>
-  <si>
-    <t>彩色文字Save</t>
-  </si>
-  <si>
-    <t>彩色文字Get</t>
-  </si>
-  <si>
-    <t>彩色文字Talk</t>
-  </si>
-  <si>
-    <t>彩色文字Quest</t>
-  </si>
-  <si>
-    <t>彩色文字Event</t>
-  </si>
-  <si>
-    <t>彩色文字warp</t>
-  </si>
-  <si>
-    <t>彩色文字Battle</t>
-  </si>
-  <si>
-    <t>彩色文字Action</t>
   </si>
 </sst>
 </file>
@@ -1030,10 +1031,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -1047,10 +1048,10 @@
         <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -1058,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1075,7 +1076,7 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -1092,7 +1093,7 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -1109,7 +1110,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -1126,7 +1127,7 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>176</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -1143,7 +1144,7 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>174</v>
       </c>
       <c r="C9">
         <v>5</v>
@@ -1160,7 +1161,7 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C10">
         <v>6</v>
@@ -1177,7 +1178,7 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C11">
         <v>7</v>
@@ -1194,7 +1195,7 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12">
         <v>8</v>
@@ -1211,7 +1212,7 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C13">
         <v>9</v>
@@ -1228,7 +1229,7 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C14">
         <v>10</v>
@@ -1245,7 +1246,7 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C15">
         <v>11</v>
@@ -1262,7 +1263,7 @@
         <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C16">
         <v>12</v>
@@ -1279,7 +1280,7 @@
         <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C17">
         <v>13</v>
@@ -1296,7 +1297,7 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C18">
         <v>14</v>
@@ -1313,7 +1314,7 @@
         <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C19">
         <v>15</v>
@@ -1330,7 +1331,7 @@
         <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C20">
         <v>16</v>
@@ -1381,7 +1382,7 @@
         <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C23">
         <v>19</v>
@@ -1398,7 +1399,7 @@
         <v>20</v>
       </c>
       <c r="B24" t="s">
-        <v>8</v>
+        <v>172</v>
       </c>
       <c r="C24">
         <v>20</v>
@@ -1415,7 +1416,7 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C25">
         <v>21</v>
@@ -1432,7 +1433,7 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C26">
         <v>22</v>
@@ -1449,7 +1450,7 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C27">
         <v>23</v>
@@ -1466,7 +1467,7 @@
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C28">
         <v>24</v>
@@ -1483,7 +1484,7 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C29">
         <v>25</v>
@@ -1500,7 +1501,7 @@
         <v>26</v>
       </c>
       <c r="B30" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C30">
         <v>26</v>
@@ -1517,7 +1518,7 @@
         <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C31">
         <v>27</v>
@@ -1534,7 +1535,7 @@
         <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C32">
         <v>28</v>
@@ -1551,7 +1552,7 @@
         <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C33">
         <v>29</v>
@@ -1568,7 +1569,7 @@
         <v>30</v>
       </c>
       <c r="B34" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C34">
         <v>30</v>
@@ -1585,7 +1586,7 @@
         <v>31</v>
       </c>
       <c r="B35" t="s">
-        <v>37</v>
+        <v>175</v>
       </c>
       <c r="C35">
         <v>31</v>
@@ -1602,7 +1603,7 @@
         <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C36">
         <v>32</v>
@@ -1619,7 +1620,7 @@
         <v>33</v>
       </c>
       <c r="B37" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C37">
         <v>33</v>
@@ -1636,7 +1637,7 @@
         <v>34</v>
       </c>
       <c r="B38" t="s">
-        <v>40</v>
+        <v>171</v>
       </c>
       <c r="C38">
         <v>34</v>
@@ -1653,7 +1654,7 @@
         <v>35</v>
       </c>
       <c r="B39" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C39">
         <v>35</v>
@@ -1670,7 +1671,7 @@
         <v>36</v>
       </c>
       <c r="B40" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C40">
         <v>36</v>
@@ -1687,7 +1688,7 @@
         <v>37</v>
       </c>
       <c r="B41" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C41">
         <v>37</v>
@@ -1704,7 +1705,7 @@
         <v>38</v>
       </c>
       <c r="B42" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C42">
         <v>38</v>
@@ -1721,7 +1722,7 @@
         <v>39</v>
       </c>
       <c r="B43" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C43">
         <v>39</v>
@@ -1738,7 +1739,7 @@
         <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C44">
         <v>40</v>
@@ -1755,7 +1756,7 @@
         <v>41</v>
       </c>
       <c r="B45" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C45">
         <v>41</v>
@@ -1772,7 +1773,7 @@
         <v>42</v>
       </c>
       <c r="B46" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C46">
         <v>42</v>
@@ -1789,7 +1790,7 @@
         <v>43</v>
       </c>
       <c r="B47" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C47">
         <v>43</v>
@@ -1806,7 +1807,7 @@
         <v>44</v>
       </c>
       <c r="B48" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C48">
         <v>44</v>
@@ -1823,7 +1824,7 @@
         <v>45</v>
       </c>
       <c r="B49" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C49">
         <v>45</v>
@@ -1840,7 +1841,7 @@
         <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C50">
         <v>46</v>
@@ -1857,7 +1858,7 @@
         <v>47</v>
       </c>
       <c r="B51" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C51">
         <v>47</v>
@@ -1874,7 +1875,7 @@
         <v>48</v>
       </c>
       <c r="B52" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C52">
         <v>48</v>
@@ -1891,7 +1892,7 @@
         <v>49</v>
       </c>
       <c r="B53" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C53">
         <v>49</v>
@@ -1908,7 +1909,7 @@
         <v>50</v>
       </c>
       <c r="B54" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C54">
         <v>50</v>
@@ -1925,7 +1926,7 @@
         <v>51</v>
       </c>
       <c r="B55" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C55">
         <v>51</v>
@@ -1942,7 +1943,7 @@
         <v>52</v>
       </c>
       <c r="B56" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C56">
         <v>52</v>
@@ -1959,7 +1960,7 @@
         <v>53</v>
       </c>
       <c r="B57" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C57">
         <v>53</v>
@@ -1976,7 +1977,7 @@
         <v>54</v>
       </c>
       <c r="B58" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C58">
         <v>54</v>
@@ -1993,7 +1994,7 @@
         <v>55</v>
       </c>
       <c r="B59" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C59">
         <v>55</v>
@@ -2010,7 +2011,7 @@
         <v>56</v>
       </c>
       <c r="B60" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C60">
         <v>56</v>
@@ -2027,7 +2028,7 @@
         <v>57</v>
       </c>
       <c r="B61" t="s">
-        <v>68</v>
+        <v>178</v>
       </c>
       <c r="C61">
         <v>57</v>
@@ -2044,7 +2045,7 @@
         <v>58</v>
       </c>
       <c r="B62" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C62">
         <v>58</v>
@@ -2061,7 +2062,7 @@
         <v>59</v>
       </c>
       <c r="B63" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C63">
         <v>59</v>
@@ -2078,7 +2079,7 @@
         <v>60</v>
       </c>
       <c r="B64" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C64">
         <v>60</v>
@@ -2095,7 +2096,7 @@
         <v>61</v>
       </c>
       <c r="B65" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C65">
         <v>61</v>
@@ -2112,7 +2113,7 @@
         <v>62</v>
       </c>
       <c r="B66" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C66">
         <v>62</v>
@@ -2129,7 +2130,7 @@
         <v>63</v>
       </c>
       <c r="B67" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C67">
         <v>63</v>
@@ -2146,7 +2147,7 @@
         <v>64</v>
       </c>
       <c r="B68" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C68">
         <v>64</v>
@@ -2163,7 +2164,7 @@
         <v>65</v>
       </c>
       <c r="B69" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C69">
         <v>65</v>
@@ -2180,7 +2181,7 @@
         <v>66</v>
       </c>
       <c r="B70" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C70">
         <v>66</v>
@@ -2197,7 +2198,7 @@
         <v>67</v>
       </c>
       <c r="B71" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C71">
         <v>67</v>
@@ -2214,7 +2215,7 @@
         <v>68</v>
       </c>
       <c r="B72" t="s">
-        <v>79</v>
+        <v>179</v>
       </c>
       <c r="C72">
         <v>68</v>
@@ -2231,7 +2232,7 @@
         <v>69</v>
       </c>
       <c r="B73" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C73">
         <v>69</v>
@@ -2248,7 +2249,7 @@
         <v>70</v>
       </c>
       <c r="B74" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C74">
         <v>70</v>
@@ -2265,7 +2266,7 @@
         <v>71</v>
       </c>
       <c r="B75" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C75">
         <v>71</v>
@@ -2282,7 +2283,7 @@
         <v>72</v>
       </c>
       <c r="B76" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C76">
         <v>72</v>
@@ -2299,7 +2300,7 @@
         <v>73</v>
       </c>
       <c r="B77" t="s">
-        <v>85</v>
+        <v>177</v>
       </c>
       <c r="C77">
         <v>73</v>
@@ -2316,7 +2317,7 @@
         <v>74</v>
       </c>
       <c r="B78" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C78">
         <v>74</v>
@@ -2333,7 +2334,7 @@
         <v>75</v>
       </c>
       <c r="B79" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C79">
         <v>75</v>
@@ -2350,7 +2351,7 @@
         <v>76</v>
       </c>
       <c r="B80" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C80">
         <v>76</v>
@@ -2367,7 +2368,7 @@
         <v>77</v>
       </c>
       <c r="B81" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C81">
         <v>77</v>
@@ -2384,7 +2385,7 @@
         <v>78</v>
       </c>
       <c r="B82" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C82">
         <v>78</v>
@@ -2401,7 +2402,7 @@
         <v>79</v>
       </c>
       <c r="B83" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C83">
         <v>79</v>
@@ -2418,7 +2419,7 @@
         <v>80</v>
       </c>
       <c r="B84" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C84">
         <v>80</v>
@@ -2435,7 +2436,7 @@
         <v>81</v>
       </c>
       <c r="B85" t="s">
-        <v>91</v>
+        <v>173</v>
       </c>
       <c r="C85">
         <v>81</v>
@@ -2452,7 +2453,7 @@
         <v>82</v>
       </c>
       <c r="B86" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C86">
         <v>82</v>
@@ -2469,7 +2470,7 @@
         <v>83</v>
       </c>
       <c r="B87" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="C87">
         <v>83</v>
@@ -2486,7 +2487,7 @@
         <v>84</v>
       </c>
       <c r="B88" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C88">
         <v>84</v>
@@ -2503,7 +2504,7 @@
         <v>85</v>
       </c>
       <c r="B89" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="C89">
         <v>85</v>
@@ -2520,7 +2521,7 @@
         <v>86</v>
       </c>
       <c r="B90" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="C90">
         <v>86</v>
@@ -2537,7 +2538,7 @@
         <v>87</v>
       </c>
       <c r="B91" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="C91">
         <v>87</v>
@@ -2554,7 +2555,7 @@
         <v>88</v>
       </c>
       <c r="B92" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C92">
         <v>88</v>
@@ -2571,7 +2572,7 @@
         <v>89</v>
       </c>
       <c r="B93" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C93">
         <v>89</v>
@@ -2588,7 +2589,7 @@
         <v>90</v>
       </c>
       <c r="B94" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="C94">
         <v>90</v>
@@ -2605,7 +2606,7 @@
         <v>91</v>
       </c>
       <c r="B95" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C95">
         <v>91</v>
@@ -2622,7 +2623,7 @@
         <v>92</v>
       </c>
       <c r="B96" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="C96">
         <v>92</v>
@@ -2639,7 +2640,7 @@
         <v>93</v>
       </c>
       <c r="B97" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="C97">
         <v>93</v>
@@ -2656,7 +2657,7 @@
         <v>94</v>
       </c>
       <c r="B98" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="C98">
         <v>94</v>
@@ -2673,7 +2674,7 @@
         <v>95</v>
       </c>
       <c r="B99" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C99">
         <v>95</v>
@@ -2690,7 +2691,7 @@
         <v>96</v>
       </c>
       <c r="B100" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="C100">
         <v>96</v>
@@ -2707,7 +2708,7 @@
         <v>97</v>
       </c>
       <c r="B101" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="C101">
         <v>97</v>
@@ -2724,7 +2725,7 @@
         <v>98</v>
       </c>
       <c r="B102" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="C102">
         <v>98</v>
@@ -2741,7 +2742,7 @@
         <v>99</v>
       </c>
       <c r="B103" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="C103">
         <v>99</v>
@@ -2928,7 +2929,7 @@
         <v>110</v>
       </c>
       <c r="B114" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="C114">
         <v>110</v>
@@ -2945,7 +2946,7 @@
         <v>111</v>
       </c>
       <c r="B115" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="C115">
         <v>111</v>
@@ -2962,7 +2963,7 @@
         <v>112</v>
       </c>
       <c r="B116" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="C116">
         <v>112</v>
@@ -2979,7 +2980,7 @@
         <v>113</v>
       </c>
       <c r="B117" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="C117">
         <v>113</v>
@@ -2996,7 +2997,7 @@
         <v>114</v>
       </c>
       <c r="B118" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="C118">
         <v>114</v>
@@ -3013,7 +3014,7 @@
         <v>115</v>
       </c>
       <c r="B119" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="C119">
         <v>115</v>
@@ -3030,7 +3031,7 @@
         <v>116</v>
       </c>
       <c r="B120" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="C120">
         <v>116</v>
@@ -3047,7 +3048,7 @@
         <v>117</v>
       </c>
       <c r="B121" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C121">
         <v>117</v>
@@ -3064,7 +3065,7 @@
         <v>118</v>
       </c>
       <c r="B122" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="C122">
         <v>118</v>
@@ -3081,7 +3082,7 @@
         <v>119</v>
       </c>
       <c r="B123" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="C123">
         <v>119</v>
@@ -3098,7 +3099,7 @@
         <v>120</v>
       </c>
       <c r="B124" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="C124">
         <v>120</v>
@@ -3115,7 +3116,7 @@
         <v>121</v>
       </c>
       <c r="B125" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="C125">
         <v>121</v>
@@ -3132,7 +3133,7 @@
         <v>122</v>
       </c>
       <c r="B126" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C126">
         <v>122</v>
@@ -3149,7 +3150,7 @@
         <v>123</v>
       </c>
       <c r="B127" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C127">
         <v>123</v>
@@ -3166,7 +3167,7 @@
         <v>124</v>
       </c>
       <c r="B128" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="C128">
         <v>124</v>
@@ -3183,7 +3184,7 @@
         <v>125</v>
       </c>
       <c r="B129" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C129">
         <v>125</v>
@@ -3200,7 +3201,7 @@
         <v>126</v>
       </c>
       <c r="B130" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="C130">
         <v>126</v>
@@ -3217,7 +3218,7 @@
         <v>127</v>
       </c>
       <c r="B131" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="C131">
         <v>127</v>
@@ -3234,7 +3235,7 @@
         <v>128</v>
       </c>
       <c r="B132" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="C132">
         <v>128</v>
@@ -3251,7 +3252,7 @@
         <v>129</v>
       </c>
       <c r="B133" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="C133">
         <v>129</v>
@@ -3268,7 +3269,7 @@
         <v>130</v>
       </c>
       <c r="B134" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="C134">
         <v>130</v>
@@ -3285,7 +3286,7 @@
         <v>131</v>
       </c>
       <c r="B135" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C135">
         <v>131</v>
@@ -3302,7 +3303,7 @@
         <v>132</v>
       </c>
       <c r="B136" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="C136">
         <v>132</v>
@@ -3319,7 +3320,7 @@
         <v>133</v>
       </c>
       <c r="B137" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="C137">
         <v>133</v>
@@ -3336,7 +3337,7 @@
         <v>134</v>
       </c>
       <c r="B138" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="C138">
         <v>134</v>
@@ -3353,7 +3354,7 @@
         <v>135</v>
       </c>
       <c r="B139" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="C139">
         <v>135</v>
@@ -3370,7 +3371,7 @@
         <v>136</v>
       </c>
       <c r="B140" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="C140">
         <v>136</v>
@@ -3387,7 +3388,7 @@
         <v>137</v>
       </c>
       <c r="B141" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="C141">
         <v>137</v>
@@ -3404,7 +3405,7 @@
         <v>138</v>
       </c>
       <c r="B142" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="C142">
         <v>138</v>
@@ -3421,7 +3422,7 @@
         <v>139</v>
       </c>
       <c r="B143" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="C143">
         <v>139</v>
@@ -3438,7 +3439,7 @@
         <v>140</v>
       </c>
       <c r="B144" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="C144">
         <v>140</v>
@@ -3455,7 +3456,7 @@
         <v>141</v>
       </c>
       <c r="B145" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="C145">
         <v>141</v>
@@ -3472,7 +3473,7 @@
         <v>142</v>
       </c>
       <c r="B146" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="C146">
         <v>142</v>
@@ -3489,7 +3490,7 @@
         <v>143</v>
       </c>
       <c r="B147" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="C147">
         <v>143</v>
@@ -3506,7 +3507,7 @@
         <v>144</v>
       </c>
       <c r="B148" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="C148">
         <v>144</v>
@@ -3523,7 +3524,7 @@
         <v>145</v>
       </c>
       <c r="B149" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="C149">
         <v>145</v>
@@ -3540,7 +3541,7 @@
         <v>146</v>
       </c>
       <c r="B150" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="C150">
         <v>146</v>
@@ -3557,7 +3558,7 @@
         <v>147</v>
       </c>
       <c r="B151" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C151">
         <v>147</v>
@@ -3574,7 +3575,7 @@
         <v>148</v>
       </c>
       <c r="B152" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="C152">
         <v>148</v>
@@ -3591,7 +3592,7 @@
         <v>149</v>
       </c>
       <c r="B153" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="C153">
         <v>149</v>
@@ -3608,7 +3609,7 @@
         <v>150</v>
       </c>
       <c r="B154" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="C154">
         <v>150</v>
@@ -3625,7 +3626,7 @@
         <v>151</v>
       </c>
       <c r="B155" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="C155">
         <v>151</v>
@@ -3642,7 +3643,7 @@
         <v>152</v>
       </c>
       <c r="B156" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="C156">
         <v>152</v>
@@ -3659,7 +3660,7 @@
         <v>153</v>
       </c>
       <c r="B157" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="C157">
         <v>153</v>
@@ -3676,7 +3677,7 @@
         <v>154</v>
       </c>
       <c r="B158" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="C158">
         <v>154</v>
@@ -3693,7 +3694,7 @@
         <v>155</v>
       </c>
       <c r="B159" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="C159">
         <v>155</v>
@@ -3710,7 +3711,7 @@
         <v>156</v>
       </c>
       <c r="B160" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="C160">
         <v>156</v>
@@ -3727,7 +3728,7 @@
         <v>157</v>
       </c>
       <c r="B161" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="C161">
         <v>157</v>
@@ -3744,7 +3745,7 @@
         <v>158</v>
       </c>
       <c r="B162" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="C162">
         <v>158</v>
@@ -3761,7 +3762,7 @@
         <v>159</v>
       </c>
       <c r="B163" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="C163">
         <v>159</v>
@@ -3778,7 +3779,7 @@
         <v>160</v>
       </c>
       <c r="B164" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="C164">
         <v>160</v>
@@ -3795,7 +3796,7 @@
         <v>161</v>
       </c>
       <c r="B165" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="C165">
         <v>161</v>
@@ -3812,7 +3813,7 @@
         <v>162</v>
       </c>
       <c r="B166" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="C166">
         <v>162</v>
@@ -3829,7 +3830,7 @@
         <v>163</v>
       </c>
       <c r="B167" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="C167">
         <v>163</v>
@@ -3846,7 +3847,7 @@
         <v>164</v>
       </c>
       <c r="B168" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C168">
         <v>164</v>
@@ -3863,7 +3864,7 @@
         <v>165</v>
       </c>
       <c r="B169" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="C169">
         <v>165</v>
@@ -3880,7 +3881,7 @@
         <v>166</v>
       </c>
       <c r="B170" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="C170">
         <v>166</v>
@@ -3897,7 +3898,7 @@
         <v>167</v>
       </c>
       <c r="B171" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="C171">
         <v>167</v>
@@ -3914,7 +3915,7 @@
         <v>168</v>
       </c>
       <c r="B172" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="C172">
         <v>168</v>
@@ -3931,7 +3932,7 @@
         <v>169</v>
       </c>
       <c r="B173" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="C173">
         <v>169</v>
@@ -3948,7 +3949,7 @@
         <v>170</v>
       </c>
       <c r="B174" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="C174">
         <v>170</v>
@@ -3965,7 +3966,7 @@
         <v>171</v>
       </c>
       <c r="B175" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="C175">
         <v>171</v>
@@ -3982,7 +3983,7 @@
         <v>172</v>
       </c>
       <c r="B176" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="C176">
         <v>172</v>
@@ -3999,7 +4000,7 @@
         <v>173</v>
       </c>
       <c r="B177" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="C177">
         <v>173</v>
@@ -4016,7 +4017,7 @@
         <v>174</v>
       </c>
       <c r="B178" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="C178">
         <v>174</v>
@@ -4033,7 +4034,7 @@
         <v>175</v>
       </c>
       <c r="B179" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="C179">
         <v>175</v>
@@ -4050,7 +4051,7 @@
         <v>176</v>
       </c>
       <c r="B180" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="C180">
         <v>176</v>
@@ -4067,7 +4068,7 @@
         <v>177</v>
       </c>
       <c r="B181" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="C181">
         <v>177</v>
@@ -4084,7 +4085,7 @@
         <v>178</v>
       </c>
       <c r="B182" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="C182">
         <v>178</v>
@@ -4101,7 +4102,7 @@
         <v>179</v>
       </c>
       <c r="B183" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="C183">
         <v>179</v>

--- a/Datas/EmoteData.xlsx
+++ b/Datas/EmoteData.xlsx
@@ -1068,7 +1068,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -1085,7 +1085,7 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -1102,7 +1102,7 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -1119,7 +1119,7 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -1136,7 +1136,7 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -1153,7 +1153,7 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
@@ -1170,7 +1170,7 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
@@ -1187,7 +1187,7 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
@@ -1204,7 +1204,7 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
@@ -1221,7 +1221,7 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
@@ -1238,7 +1238,7 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
@@ -1255,7 +1255,7 @@
         <v>0</v>
       </c>
       <c r="E15">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
@@ -1272,7 +1272,7 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
@@ -1289,7 +1289,7 @@
         <v>0</v>
       </c>
       <c r="E17">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
@@ -1306,7 +1306,7 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
@@ -1323,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
@@ -1340,7 +1340,7 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="E21">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
@@ -1374,7 +1374,7 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
@@ -1391,7 +1391,7 @@
         <v>0</v>
       </c>
       <c r="E23">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
@@ -1408,7 +1408,7 @@
         <v>0</v>
       </c>
       <c r="E24">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
@@ -1425,7 +1425,7 @@
         <v>0</v>
       </c>
       <c r="E25">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
@@ -1442,7 +1442,7 @@
         <v>0</v>
       </c>
       <c r="E26">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="E27">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
@@ -1476,7 +1476,7 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
@@ -1493,7 +1493,7 @@
         <v>0</v>
       </c>
       <c r="E29">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
@@ -1510,7 +1510,7 @@
         <v>0</v>
       </c>
       <c r="E30">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
@@ -1527,7 +1527,7 @@
         <v>0</v>
       </c>
       <c r="E31">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
@@ -1544,7 +1544,7 @@
         <v>0</v>
       </c>
       <c r="E32">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
@@ -1561,7 +1561,7 @@
         <v>0</v>
       </c>
       <c r="E33">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
@@ -1578,7 +1578,7 @@
         <v>0</v>
       </c>
       <c r="E34">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
@@ -1595,7 +1595,7 @@
         <v>0</v>
       </c>
       <c r="E35">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
@@ -1612,7 +1612,7 @@
         <v>0</v>
       </c>
       <c r="E36">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="E37">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
@@ -1646,7 +1646,7 @@
         <v>0</v>
       </c>
       <c r="E38">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
@@ -1663,7 +1663,7 @@
         <v>0</v>
       </c>
       <c r="E39">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="E40">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
@@ -1697,7 +1697,7 @@
         <v>0</v>
       </c>
       <c r="E41">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
@@ -1714,7 +1714,7 @@
         <v>0</v>
       </c>
       <c r="E42">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
@@ -1731,7 +1731,7 @@
         <v>0</v>
       </c>
       <c r="E43">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
@@ -1748,7 +1748,7 @@
         <v>0</v>
       </c>
       <c r="E44">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
@@ -1765,7 +1765,7 @@
         <v>0</v>
       </c>
       <c r="E45">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
@@ -1782,7 +1782,7 @@
         <v>0</v>
       </c>
       <c r="E46">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="E47">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
@@ -1816,7 +1816,7 @@
         <v>0</v>
       </c>
       <c r="E48">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
@@ -1833,7 +1833,7 @@
         <v>0</v>
       </c>
       <c r="E49">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
@@ -1850,7 +1850,7 @@
         <v>0</v>
       </c>
       <c r="E50">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
@@ -1867,7 +1867,7 @@
         <v>0</v>
       </c>
       <c r="E51">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
@@ -1884,7 +1884,7 @@
         <v>0</v>
       </c>
       <c r="E52">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
@@ -1901,7 +1901,7 @@
         <v>0</v>
       </c>
       <c r="E53">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
@@ -1918,7 +1918,7 @@
         <v>0</v>
       </c>
       <c r="E54">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
@@ -1935,7 +1935,7 @@
         <v>0</v>
       </c>
       <c r="E55">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
@@ -1952,7 +1952,7 @@
         <v>0</v>
       </c>
       <c r="E56">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
@@ -1969,7 +1969,7 @@
         <v>0</v>
       </c>
       <c r="E57">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
@@ -1986,7 +1986,7 @@
         <v>0</v>
       </c>
       <c r="E58">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
@@ -2003,7 +2003,7 @@
         <v>0</v>
       </c>
       <c r="E59">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
@@ -2020,7 +2020,7 @@
         <v>0</v>
       </c>
       <c r="E60">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
@@ -2037,7 +2037,7 @@
         <v>0</v>
       </c>
       <c r="E61">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
@@ -2054,7 +2054,7 @@
         <v>0</v>
       </c>
       <c r="E62">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
@@ -2071,7 +2071,7 @@
         <v>0</v>
       </c>
       <c r="E63">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
@@ -2088,7 +2088,7 @@
         <v>0</v>
       </c>
       <c r="E64">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
@@ -2105,7 +2105,7 @@
         <v>0</v>
       </c>
       <c r="E65">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
@@ -2122,7 +2122,7 @@
         <v>0</v>
       </c>
       <c r="E66">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="E67">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
@@ -2156,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="E68">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
@@ -2173,7 +2173,7 @@
         <v>0</v>
       </c>
       <c r="E69">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
@@ -2190,7 +2190,7 @@
         <v>0</v>
       </c>
       <c r="E70">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
@@ -2207,7 +2207,7 @@
         <v>0</v>
       </c>
       <c r="E71">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
@@ -2224,7 +2224,7 @@
         <v>0</v>
       </c>
       <c r="E72">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.2">
@@ -2241,7 +2241,7 @@
         <v>0</v>
       </c>
       <c r="E73">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
@@ -2258,7 +2258,7 @@
         <v>0</v>
       </c>
       <c r="E74">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
@@ -2275,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="E75">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
@@ -2292,7 +2292,7 @@
         <v>0</v>
       </c>
       <c r="E76">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.2">
@@ -2309,7 +2309,7 @@
         <v>0</v>
       </c>
       <c r="E77">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
@@ -2326,7 +2326,7 @@
         <v>0</v>
       </c>
       <c r="E78">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.2">
@@ -2343,7 +2343,7 @@
         <v>0</v>
       </c>
       <c r="E79">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.2">
@@ -2360,7 +2360,7 @@
         <v>0</v>
       </c>
       <c r="E80">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.2">
@@ -2377,7 +2377,7 @@
         <v>0</v>
       </c>
       <c r="E81">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
@@ -2394,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="E82">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.2">
@@ -2411,7 +2411,7 @@
         <v>0</v>
       </c>
       <c r="E83">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
@@ -2428,7 +2428,7 @@
         <v>0</v>
       </c>
       <c r="E84">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.2">
@@ -2445,7 +2445,7 @@
         <v>0</v>
       </c>
       <c r="E85">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.2">
@@ -2462,7 +2462,7 @@
         <v>0</v>
       </c>
       <c r="E86">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.2">
@@ -2479,7 +2479,7 @@
         <v>0</v>
       </c>
       <c r="E87">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.2">
@@ -2496,7 +2496,7 @@
         <v>0</v>
       </c>
       <c r="E88">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.2">
@@ -2513,7 +2513,7 @@
         <v>0</v>
       </c>
       <c r="E89">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.2">
@@ -2530,7 +2530,7 @@
         <v>0</v>
       </c>
       <c r="E90">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.2">
@@ -2547,7 +2547,7 @@
         <v>0</v>
       </c>
       <c r="E91">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.2">
@@ -2564,7 +2564,7 @@
         <v>0</v>
       </c>
       <c r="E92">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.2">
@@ -2581,7 +2581,7 @@
         <v>0</v>
       </c>
       <c r="E93">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.2">
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="E94">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.2">
@@ -2615,7 +2615,7 @@
         <v>0</v>
       </c>
       <c r="E95">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.2">
@@ -2632,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="E96">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.2">
@@ -2649,7 +2649,7 @@
         <v>0</v>
       </c>
       <c r="E97">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.2">
@@ -2666,7 +2666,7 @@
         <v>0</v>
       </c>
       <c r="E98">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.2">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="E99">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.2">
@@ -2700,7 +2700,7 @@
         <v>0</v>
       </c>
       <c r="E100">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.2">
@@ -2717,7 +2717,7 @@
         <v>0</v>
       </c>
       <c r="E101">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.2">
@@ -2734,7 +2734,7 @@
         <v>0</v>
       </c>
       <c r="E102">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.2">
@@ -2751,7 +2751,7 @@
         <v>0</v>
       </c>
       <c r="E103">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.2">
@@ -2768,7 +2768,7 @@
         <v>0</v>
       </c>
       <c r="E104">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.2">
@@ -2785,7 +2785,7 @@
         <v>0</v>
       </c>
       <c r="E105">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.2">
@@ -2802,7 +2802,7 @@
         <v>0</v>
       </c>
       <c r="E106">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.2">
@@ -2819,7 +2819,7 @@
         <v>0</v>
       </c>
       <c r="E107">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.2">
@@ -2836,7 +2836,7 @@
         <v>0</v>
       </c>
       <c r="E108">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.2">
@@ -2853,7 +2853,7 @@
         <v>0</v>
       </c>
       <c r="E109">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.2">
@@ -2870,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="E110">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.2">
@@ -2887,7 +2887,7 @@
         <v>0</v>
       </c>
       <c r="E111">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.2">
@@ -2904,7 +2904,7 @@
         <v>0</v>
       </c>
       <c r="E112">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.2">
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="E113">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.2">
@@ -2938,7 +2938,7 @@
         <v>0</v>
       </c>
       <c r="E114">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.2">
@@ -2955,7 +2955,7 @@
         <v>0</v>
       </c>
       <c r="E115">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.2">
@@ -2972,7 +2972,7 @@
         <v>0</v>
       </c>
       <c r="E116">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.2">
@@ -2989,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="E117">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.2">
@@ -3006,7 +3006,7 @@
         <v>0</v>
       </c>
       <c r="E118">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.2">
@@ -3023,7 +3023,7 @@
         <v>0</v>
       </c>
       <c r="E119">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.2">
@@ -3040,7 +3040,7 @@
         <v>0</v>
       </c>
       <c r="E120">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.2">
@@ -3057,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="E121">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.2">
@@ -3074,7 +3074,7 @@
         <v>0</v>
       </c>
       <c r="E122">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.2">
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="E123">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.2">
@@ -3108,7 +3108,7 @@
         <v>0</v>
       </c>
       <c r="E124">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.2">
@@ -3125,7 +3125,7 @@
         <v>0</v>
       </c>
       <c r="E125">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.2">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="E126">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.2">
@@ -3159,7 +3159,7 @@
         <v>0</v>
       </c>
       <c r="E127">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.2">
@@ -3176,7 +3176,7 @@
         <v>0</v>
       </c>
       <c r="E128">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.2">
@@ -3193,7 +3193,7 @@
         <v>0</v>
       </c>
       <c r="E129">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.2">
@@ -3210,7 +3210,7 @@
         <v>0</v>
       </c>
       <c r="E130">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.2">
@@ -3227,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="E131">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.2">
@@ -3244,7 +3244,7 @@
         <v>0</v>
       </c>
       <c r="E132">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.2">
@@ -3261,7 +3261,7 @@
         <v>0</v>
       </c>
       <c r="E133">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.2">
@@ -3278,7 +3278,7 @@
         <v>0</v>
       </c>
       <c r="E134">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.2">
@@ -3295,7 +3295,7 @@
         <v>0</v>
       </c>
       <c r="E135">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.2">
@@ -3312,7 +3312,7 @@
         <v>0</v>
       </c>
       <c r="E136">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.2">
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="E137">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.2">
@@ -3346,7 +3346,7 @@
         <v>0</v>
       </c>
       <c r="E138">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.2">
@@ -3363,7 +3363,7 @@
         <v>0</v>
       </c>
       <c r="E139">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.2">
@@ -3380,7 +3380,7 @@
         <v>0</v>
       </c>
       <c r="E140">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.2">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="E141">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.2">
@@ -3414,7 +3414,7 @@
         <v>0</v>
       </c>
       <c r="E142">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.2">
@@ -3431,7 +3431,7 @@
         <v>0</v>
       </c>
       <c r="E143">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.2">
@@ -3448,7 +3448,7 @@
         <v>0</v>
       </c>
       <c r="E144">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.2">
@@ -3465,7 +3465,7 @@
         <v>0</v>
       </c>
       <c r="E145">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.2">
@@ -3482,7 +3482,7 @@
         <v>0</v>
       </c>
       <c r="E146">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.2">
@@ -3499,7 +3499,7 @@
         <v>0</v>
       </c>
       <c r="E147">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.2">
@@ -3516,7 +3516,7 @@
         <v>0</v>
       </c>
       <c r="E148">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.2">
@@ -3533,7 +3533,7 @@
         <v>0</v>
       </c>
       <c r="E149">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.2">
@@ -3550,7 +3550,7 @@
         <v>0</v>
       </c>
       <c r="E150">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.2">
@@ -3567,7 +3567,7 @@
         <v>0</v>
       </c>
       <c r="E151">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.2">
@@ -3584,7 +3584,7 @@
         <v>0</v>
       </c>
       <c r="E152">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.2">
@@ -3601,7 +3601,7 @@
         <v>0</v>
       </c>
       <c r="E153">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.2">
@@ -3618,7 +3618,7 @@
         <v>0</v>
       </c>
       <c r="E154">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.2">
@@ -3635,7 +3635,7 @@
         <v>0</v>
       </c>
       <c r="E155">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.2">
@@ -3652,7 +3652,7 @@
         <v>0</v>
       </c>
       <c r="E156">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.2">
@@ -3669,7 +3669,7 @@
         <v>0</v>
       </c>
       <c r="E157">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.2">
@@ -3686,7 +3686,7 @@
         <v>0</v>
       </c>
       <c r="E158">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.2">
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="E159">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.2">
@@ -3720,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="E160">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.2">
@@ -3737,7 +3737,7 @@
         <v>0</v>
       </c>
       <c r="E161">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.2">
@@ -3754,7 +3754,7 @@
         <v>0</v>
       </c>
       <c r="E162">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.2">
@@ -3771,7 +3771,7 @@
         <v>0</v>
       </c>
       <c r="E163">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.2">
@@ -3788,7 +3788,7 @@
         <v>0</v>
       </c>
       <c r="E164">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.2">
@@ -3805,7 +3805,7 @@
         <v>0</v>
       </c>
       <c r="E165">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.2">
@@ -3822,7 +3822,7 @@
         <v>0</v>
       </c>
       <c r="E166">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.2">
@@ -3839,7 +3839,7 @@
         <v>0</v>
       </c>
       <c r="E167">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.2">
@@ -3856,7 +3856,7 @@
         <v>0</v>
       </c>
       <c r="E168">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.2">
@@ -3873,7 +3873,7 @@
         <v>0</v>
       </c>
       <c r="E169">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.2">
@@ -3890,7 +3890,7 @@
         <v>0</v>
       </c>
       <c r="E170">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.2">
@@ -3907,7 +3907,7 @@
         <v>0</v>
       </c>
       <c r="E171">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.2">
@@ -3924,7 +3924,7 @@
         <v>0</v>
       </c>
       <c r="E172">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.2">
@@ -3941,7 +3941,7 @@
         <v>0</v>
       </c>
       <c r="E173">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.2">
@@ -3958,7 +3958,7 @@
         <v>0</v>
       </c>
       <c r="E174">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.2">
@@ -3975,7 +3975,7 @@
         <v>0</v>
       </c>
       <c r="E175">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.2">
@@ -3992,7 +3992,7 @@
         <v>0</v>
       </c>
       <c r="E176">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.2">
@@ -4009,7 +4009,7 @@
         <v>0</v>
       </c>
       <c r="E177">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.2">
@@ -4026,7 +4026,7 @@
         <v>0</v>
       </c>
       <c r="E178">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.2">
@@ -4043,7 +4043,7 @@
         <v>0</v>
       </c>
       <c r="E179">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.2">
@@ -4060,7 +4060,7 @@
         <v>0</v>
       </c>
       <c r="E180">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.2">
@@ -4077,7 +4077,7 @@
         <v>0</v>
       </c>
       <c r="E181">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.2">
@@ -4094,7 +4094,7 @@
         <v>0</v>
       </c>
       <c r="E182">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.2">
@@ -4111,7 +4111,7 @@
         <v>0</v>
       </c>
       <c r="E183">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/EmoteData.xlsx
+++ b/Datas/EmoteData.xlsx
@@ -1068,7 +1068,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -1085,7 +1085,7 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -1102,7 +1102,7 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -1119,7 +1119,7 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -1136,7 +1136,7 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -1153,7 +1153,7 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
@@ -1170,7 +1170,7 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
@@ -1187,7 +1187,7 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
@@ -1204,7 +1204,7 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
@@ -1221,7 +1221,7 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
@@ -1238,7 +1238,7 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
@@ -1255,7 +1255,7 @@
         <v>0</v>
       </c>
       <c r="E15">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
@@ -1272,7 +1272,7 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
@@ -1289,7 +1289,7 @@
         <v>0</v>
       </c>
       <c r="E17">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
@@ -1306,7 +1306,7 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
@@ -1323,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
@@ -1340,7 +1340,7 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="E21">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
@@ -1374,7 +1374,7 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
@@ -1391,7 +1391,7 @@
         <v>0</v>
       </c>
       <c r="E23">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
@@ -1408,7 +1408,7 @@
         <v>0</v>
       </c>
       <c r="E24">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
@@ -1425,7 +1425,7 @@
         <v>0</v>
       </c>
       <c r="E25">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
@@ -1442,7 +1442,7 @@
         <v>0</v>
       </c>
       <c r="E26">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="E27">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
@@ -1476,7 +1476,7 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
@@ -1493,7 +1493,7 @@
         <v>0</v>
       </c>
       <c r="E29">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
@@ -1510,7 +1510,7 @@
         <v>0</v>
       </c>
       <c r="E30">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
@@ -1527,7 +1527,7 @@
         <v>0</v>
       </c>
       <c r="E31">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
@@ -1544,7 +1544,7 @@
         <v>0</v>
       </c>
       <c r="E32">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
@@ -1561,7 +1561,7 @@
         <v>0</v>
       </c>
       <c r="E33">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
@@ -1578,7 +1578,7 @@
         <v>0</v>
       </c>
       <c r="E34">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
@@ -1595,7 +1595,7 @@
         <v>0</v>
       </c>
       <c r="E35">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
@@ -1612,7 +1612,7 @@
         <v>0</v>
       </c>
       <c r="E36">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="E37">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
@@ -1646,7 +1646,7 @@
         <v>0</v>
       </c>
       <c r="E38">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
@@ -1663,7 +1663,7 @@
         <v>0</v>
       </c>
       <c r="E39">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="E40">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
@@ -1697,7 +1697,7 @@
         <v>0</v>
       </c>
       <c r="E41">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
@@ -1714,7 +1714,7 @@
         <v>0</v>
       </c>
       <c r="E42">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
@@ -1731,7 +1731,7 @@
         <v>0</v>
       </c>
       <c r="E43">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
@@ -1748,7 +1748,7 @@
         <v>0</v>
       </c>
       <c r="E44">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
@@ -1765,7 +1765,7 @@
         <v>0</v>
       </c>
       <c r="E45">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
@@ -1782,7 +1782,7 @@
         <v>0</v>
       </c>
       <c r="E46">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="E47">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
@@ -1816,7 +1816,7 @@
         <v>0</v>
       </c>
       <c r="E48">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
@@ -1833,7 +1833,7 @@
         <v>0</v>
       </c>
       <c r="E49">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
@@ -1850,7 +1850,7 @@
         <v>0</v>
       </c>
       <c r="E50">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
@@ -1867,7 +1867,7 @@
         <v>0</v>
       </c>
       <c r="E51">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
@@ -1884,7 +1884,7 @@
         <v>0</v>
       </c>
       <c r="E52">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
@@ -1901,7 +1901,7 @@
         <v>0</v>
       </c>
       <c r="E53">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
@@ -1918,7 +1918,7 @@
         <v>0</v>
       </c>
       <c r="E54">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
@@ -1935,7 +1935,7 @@
         <v>0</v>
       </c>
       <c r="E55">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
@@ -1952,7 +1952,7 @@
         <v>0</v>
       </c>
       <c r="E56">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
@@ -1969,7 +1969,7 @@
         <v>0</v>
       </c>
       <c r="E57">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
@@ -1986,7 +1986,7 @@
         <v>0</v>
       </c>
       <c r="E58">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
@@ -2003,7 +2003,7 @@
         <v>0</v>
       </c>
       <c r="E59">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
@@ -2020,7 +2020,7 @@
         <v>0</v>
       </c>
       <c r="E60">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
@@ -2037,7 +2037,7 @@
         <v>0</v>
       </c>
       <c r="E61">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
@@ -2054,7 +2054,7 @@
         <v>0</v>
       </c>
       <c r="E62">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
@@ -2071,7 +2071,7 @@
         <v>0</v>
       </c>
       <c r="E63">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
@@ -2088,7 +2088,7 @@
         <v>0</v>
       </c>
       <c r="E64">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
@@ -2105,7 +2105,7 @@
         <v>0</v>
       </c>
       <c r="E65">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
@@ -2122,7 +2122,7 @@
         <v>0</v>
       </c>
       <c r="E66">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="E67">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
@@ -2156,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="E68">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
@@ -2173,7 +2173,7 @@
         <v>0</v>
       </c>
       <c r="E69">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
@@ -2190,7 +2190,7 @@
         <v>0</v>
       </c>
       <c r="E70">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
@@ -2207,7 +2207,7 @@
         <v>0</v>
       </c>
       <c r="E71">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
@@ -2224,7 +2224,7 @@
         <v>0</v>
       </c>
       <c r="E72">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.2">
@@ -2241,7 +2241,7 @@
         <v>0</v>
       </c>
       <c r="E73">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
@@ -2258,7 +2258,7 @@
         <v>0</v>
       </c>
       <c r="E74">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
@@ -2275,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="E75">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
@@ -2292,7 +2292,7 @@
         <v>0</v>
       </c>
       <c r="E76">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.2">
@@ -2309,7 +2309,7 @@
         <v>0</v>
       </c>
       <c r="E77">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
@@ -2326,7 +2326,7 @@
         <v>0</v>
       </c>
       <c r="E78">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.2">
@@ -2343,7 +2343,7 @@
         <v>0</v>
       </c>
       <c r="E79">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.2">
@@ -2360,7 +2360,7 @@
         <v>0</v>
       </c>
       <c r="E80">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.2">
@@ -2377,7 +2377,7 @@
         <v>0</v>
       </c>
       <c r="E81">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
@@ -2394,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="E82">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.2">
@@ -2411,7 +2411,7 @@
         <v>0</v>
       </c>
       <c r="E83">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
@@ -2428,7 +2428,7 @@
         <v>0</v>
       </c>
       <c r="E84">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.2">
@@ -2445,7 +2445,7 @@
         <v>0</v>
       </c>
       <c r="E85">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.2">
@@ -2462,7 +2462,7 @@
         <v>0</v>
       </c>
       <c r="E86">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.2">
@@ -2479,7 +2479,7 @@
         <v>0</v>
       </c>
       <c r="E87">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.2">
@@ -2496,7 +2496,7 @@
         <v>0</v>
       </c>
       <c r="E88">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.2">
@@ -2513,7 +2513,7 @@
         <v>0</v>
       </c>
       <c r="E89">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.2">
@@ -2530,7 +2530,7 @@
         <v>0</v>
       </c>
       <c r="E90">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.2">
@@ -2547,7 +2547,7 @@
         <v>0</v>
       </c>
       <c r="E91">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.2">
@@ -2564,7 +2564,7 @@
         <v>0</v>
       </c>
       <c r="E92">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.2">
@@ -2581,7 +2581,7 @@
         <v>0</v>
       </c>
       <c r="E93">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.2">
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="E94">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.2">
@@ -2615,7 +2615,7 @@
         <v>0</v>
       </c>
       <c r="E95">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.2">
@@ -2632,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="E96">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.2">
@@ -2649,7 +2649,7 @@
         <v>0</v>
       </c>
       <c r="E97">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.2">
@@ -2666,7 +2666,7 @@
         <v>0</v>
       </c>
       <c r="E98">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.2">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="E99">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.2">
@@ -2700,7 +2700,7 @@
         <v>0</v>
       </c>
       <c r="E100">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.2">
@@ -2717,7 +2717,7 @@
         <v>0</v>
       </c>
       <c r="E101">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.2">
@@ -2734,7 +2734,7 @@
         <v>0</v>
       </c>
       <c r="E102">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.2">
@@ -2751,7 +2751,7 @@
         <v>0</v>
       </c>
       <c r="E103">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.2">
@@ -2768,7 +2768,7 @@
         <v>0</v>
       </c>
       <c r="E104">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.2">
@@ -2785,7 +2785,7 @@
         <v>0</v>
       </c>
       <c r="E105">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.2">
@@ -2802,7 +2802,7 @@
         <v>0</v>
       </c>
       <c r="E106">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.2">
@@ -2819,7 +2819,7 @@
         <v>0</v>
       </c>
       <c r="E107">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.2">
@@ -2836,7 +2836,7 @@
         <v>0</v>
       </c>
       <c r="E108">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.2">
@@ -2853,7 +2853,7 @@
         <v>0</v>
       </c>
       <c r="E109">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.2">
@@ -2870,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="E110">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.2">
@@ -2887,7 +2887,7 @@
         <v>0</v>
       </c>
       <c r="E111">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.2">
@@ -2904,7 +2904,7 @@
         <v>0</v>
       </c>
       <c r="E112">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.2">
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="E113">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.2">
@@ -2938,7 +2938,7 @@
         <v>0</v>
       </c>
       <c r="E114">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.2">
@@ -2955,7 +2955,7 @@
         <v>0</v>
       </c>
       <c r="E115">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.2">
@@ -2972,7 +2972,7 @@
         <v>0</v>
       </c>
       <c r="E116">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.2">
@@ -2989,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="E117">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.2">
@@ -3006,7 +3006,7 @@
         <v>0</v>
       </c>
       <c r="E118">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.2">
@@ -3023,7 +3023,7 @@
         <v>0</v>
       </c>
       <c r="E119">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.2">
@@ -3040,7 +3040,7 @@
         <v>0</v>
       </c>
       <c r="E120">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.2">
@@ -3057,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="E121">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.2">
@@ -3074,7 +3074,7 @@
         <v>0</v>
       </c>
       <c r="E122">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.2">
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="E123">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.2">
@@ -3108,7 +3108,7 @@
         <v>0</v>
       </c>
       <c r="E124">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.2">
@@ -3125,7 +3125,7 @@
         <v>0</v>
       </c>
       <c r="E125">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.2">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="E126">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.2">
@@ -3159,7 +3159,7 @@
         <v>0</v>
       </c>
       <c r="E127">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.2">
@@ -3176,7 +3176,7 @@
         <v>0</v>
       </c>
       <c r="E128">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.2">
@@ -3193,7 +3193,7 @@
         <v>0</v>
       </c>
       <c r="E129">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.2">
@@ -3210,7 +3210,7 @@
         <v>0</v>
       </c>
       <c r="E130">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.2">
@@ -3227,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="E131">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.2">
@@ -3244,7 +3244,7 @@
         <v>0</v>
       </c>
       <c r="E132">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.2">
@@ -3261,7 +3261,7 @@
         <v>0</v>
       </c>
       <c r="E133">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.2">
@@ -3278,7 +3278,7 @@
         <v>0</v>
       </c>
       <c r="E134">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.2">
@@ -3295,7 +3295,7 @@
         <v>0</v>
       </c>
       <c r="E135">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.2">
@@ -3312,7 +3312,7 @@
         <v>0</v>
       </c>
       <c r="E136">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.2">
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="E137">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.2">
@@ -3346,7 +3346,7 @@
         <v>0</v>
       </c>
       <c r="E138">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.2">
@@ -3363,7 +3363,7 @@
         <v>0</v>
       </c>
       <c r="E139">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.2">
@@ -3380,7 +3380,7 @@
         <v>0</v>
       </c>
       <c r="E140">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.2">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="E141">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.2">
@@ -3414,7 +3414,7 @@
         <v>0</v>
       </c>
       <c r="E142">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.2">
@@ -3431,7 +3431,7 @@
         <v>0</v>
       </c>
       <c r="E143">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.2">
@@ -3448,7 +3448,7 @@
         <v>0</v>
       </c>
       <c r="E144">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.2">
@@ -3465,7 +3465,7 @@
         <v>0</v>
       </c>
       <c r="E145">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.2">
@@ -3482,7 +3482,7 @@
         <v>0</v>
       </c>
       <c r="E146">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.2">
@@ -3499,7 +3499,7 @@
         <v>0</v>
       </c>
       <c r="E147">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.2">
@@ -3516,7 +3516,7 @@
         <v>0</v>
       </c>
       <c r="E148">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.2">
@@ -3533,7 +3533,7 @@
         <v>0</v>
       </c>
       <c r="E149">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.2">
@@ -3550,7 +3550,7 @@
         <v>0</v>
       </c>
       <c r="E150">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.2">
@@ -3567,7 +3567,7 @@
         <v>0</v>
       </c>
       <c r="E151">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.2">
@@ -3584,7 +3584,7 @@
         <v>0</v>
       </c>
       <c r="E152">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.2">
@@ -3601,7 +3601,7 @@
         <v>0</v>
       </c>
       <c r="E153">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.2">
@@ -3618,7 +3618,7 @@
         <v>0</v>
       </c>
       <c r="E154">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.2">
@@ -3635,7 +3635,7 @@
         <v>0</v>
       </c>
       <c r="E155">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.2">
@@ -3652,7 +3652,7 @@
         <v>0</v>
       </c>
       <c r="E156">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.2">
@@ -3669,7 +3669,7 @@
         <v>0</v>
       </c>
       <c r="E157">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.2">
@@ -3686,7 +3686,7 @@
         <v>0</v>
       </c>
       <c r="E158">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.2">
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="E159">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.2">
@@ -3720,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="E160">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.2">
@@ -3737,7 +3737,7 @@
         <v>0</v>
       </c>
       <c r="E161">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.2">
@@ -3754,7 +3754,7 @@
         <v>0</v>
       </c>
       <c r="E162">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.2">
@@ -3771,7 +3771,7 @@
         <v>0</v>
       </c>
       <c r="E163">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.2">
@@ -3788,7 +3788,7 @@
         <v>0</v>
       </c>
       <c r="E164">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.2">
@@ -3805,7 +3805,7 @@
         <v>0</v>
       </c>
       <c r="E165">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.2">
@@ -3822,7 +3822,7 @@
         <v>0</v>
       </c>
       <c r="E166">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.2">
@@ -3839,7 +3839,7 @@
         <v>0</v>
       </c>
       <c r="E167">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.2">
@@ -3856,7 +3856,7 @@
         <v>0</v>
       </c>
       <c r="E168">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.2">
@@ -3873,7 +3873,7 @@
         <v>0</v>
       </c>
       <c r="E169">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.2">
@@ -3890,7 +3890,7 @@
         <v>0</v>
       </c>
       <c r="E170">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.2">
@@ -3907,7 +3907,7 @@
         <v>0</v>
       </c>
       <c r="E171">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.2">
@@ -3924,7 +3924,7 @@
         <v>0</v>
       </c>
       <c r="E172">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.2">
@@ -3941,7 +3941,7 @@
         <v>0</v>
       </c>
       <c r="E173">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.2">
@@ -3958,7 +3958,7 @@
         <v>0</v>
       </c>
       <c r="E174">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.2">
@@ -3975,7 +3975,7 @@
         <v>0</v>
       </c>
       <c r="E175">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.2">
@@ -3992,7 +3992,7 @@
         <v>0</v>
       </c>
       <c r="E176">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.2">
@@ -4009,7 +4009,7 @@
         <v>0</v>
       </c>
       <c r="E177">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.2">
@@ -4026,7 +4026,7 @@
         <v>0</v>
       </c>
       <c r="E178">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.2">
@@ -4043,7 +4043,7 @@
         <v>0</v>
       </c>
       <c r="E179">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.2">
@@ -4060,7 +4060,7 @@
         <v>0</v>
       </c>
       <c r="E180">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.2">
@@ -4077,7 +4077,7 @@
         <v>0</v>
       </c>
       <c r="E181">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.2">
@@ -4094,7 +4094,7 @@
         <v>0</v>
       </c>
       <c r="E182">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.2">
@@ -4111,7 +4111,7 @@
         <v>0</v>
       </c>
       <c r="E183">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
